--- a/data/raw/AMD.xlsx
+++ b/data/raw/AMD.xlsx
@@ -468,5022 +468,5022 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45834</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>143.6799926757812</v>
+        <v>134.8000030517578</v>
       </c>
       <c r="C2" t="n">
-        <v>146</v>
+        <v>137.4400024414062</v>
       </c>
       <c r="D2" t="n">
-        <v>141.9100036621094</v>
+        <v>133.5</v>
       </c>
       <c r="E2" t="n">
-        <v>145.9700012207031</v>
+        <v>136.5599975585938</v>
       </c>
       <c r="F2" t="n">
-        <v>58180100</v>
+        <v>37395000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45835</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>143.8099975585938</v>
+        <v>137.8200073242188</v>
       </c>
       <c r="C3" t="n">
-        <v>147.75</v>
+        <v>139.1499938964844</v>
       </c>
       <c r="D3" t="n">
-        <v>141.6300048828125</v>
+        <v>135.9100036621094</v>
       </c>
       <c r="E3" t="n">
-        <v>144.1799926757812</v>
+        <v>137.3200073242188</v>
       </c>
       <c r="F3" t="n">
-        <v>61937900</v>
+        <v>36124600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45838</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>141.8999938964844</v>
+        <v>138.4100036621094</v>
       </c>
       <c r="C4" t="n">
-        <v>146</v>
+        <v>140.6499938964844</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0099945068359</v>
+        <v>137.5899963378906</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>138.6900024414062</v>
       </c>
       <c r="F4" t="n">
-        <v>42972500</v>
+        <v>37013100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45839</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>136.1100006103516</v>
+        <v>144.1600036621094</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2299957275391</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="D5" t="n">
-        <v>135.1199951171875</v>
+        <v>141.8500061035156</v>
       </c>
       <c r="E5" t="n">
-        <v>138.7700042724609</v>
+        <v>143</v>
       </c>
       <c r="F5" t="n">
-        <v>55257200</v>
+        <v>61101500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>138.5200042724609</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="C6" t="n">
-        <v>139.7799987792969</v>
+        <v>147.3999938964844</v>
       </c>
       <c r="D6" t="n">
-        <v>135.2200012207031</v>
+        <v>141.6000061035156</v>
       </c>
       <c r="E6" t="n">
-        <v>135.5299987792969</v>
+        <v>142.6000061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>39228000</v>
+        <v>50049200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>137.9100036621094</v>
+        <v>146.2400054931641</v>
       </c>
       <c r="C7" t="n">
-        <v>139.5</v>
+        <v>147.5800018310547</v>
       </c>
       <c r="D7" t="n">
-        <v>137.3200073242188</v>
+        <v>141.8999938964844</v>
       </c>
       <c r="E7" t="n">
-        <v>139.1100006103516</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="F7" t="n">
-        <v>28646000</v>
+        <v>44718600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>134.8000030517578</v>
+        <v>155.6100006103516</v>
       </c>
       <c r="C8" t="n">
-        <v>137.4400024414062</v>
+        <v>158.6799926757812</v>
       </c>
       <c r="D8" t="n">
-        <v>133.5</v>
+        <v>153.5599975585938</v>
       </c>
       <c r="E8" t="n">
-        <v>136.5599975585938</v>
+        <v>153.75</v>
       </c>
       <c r="F8" t="n">
-        <v>37395000</v>
+        <v>93370100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45846</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>137.8200073242188</v>
+        <v>160.0800018310547</v>
       </c>
       <c r="C9" t="n">
-        <v>139.1499938964844</v>
+        <v>160.3600006103516</v>
       </c>
       <c r="D9" t="n">
-        <v>135.9100036621094</v>
+        <v>152.8500061035156</v>
       </c>
       <c r="E9" t="n">
-        <v>137.3200073242188</v>
+        <v>155.3099975585938</v>
       </c>
       <c r="F9" t="n">
-        <v>36124600</v>
+        <v>59492800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45847</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>138.4100036621094</v>
+        <v>160.4100036621094</v>
       </c>
       <c r="C10" t="n">
-        <v>140.6499938964844</v>
+        <v>161.9600067138672</v>
       </c>
       <c r="D10" t="n">
-        <v>137.5899963378906</v>
+        <v>158.6799926757812</v>
       </c>
       <c r="E10" t="n">
-        <v>138.6900024414062</v>
+        <v>161.8099975585938</v>
       </c>
       <c r="F10" t="n">
-        <v>37013100</v>
+        <v>50605100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>144.1600036621094</v>
+        <v>156.9900054931641</v>
       </c>
       <c r="C11" t="n">
-        <v>145.8200073242188</v>
+        <v>160.8300018310547</v>
       </c>
       <c r="D11" t="n">
-        <v>141.8500061035156</v>
+        <v>155.8099975585938</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>159.5899963378906</v>
       </c>
       <c r="F11" t="n">
-        <v>61101500</v>
+        <v>48859800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45849</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>146.4199981689453</v>
+        <v>157</v>
       </c>
       <c r="C12" t="n">
-        <v>147.3999938964844</v>
+        <v>160.3399963378906</v>
       </c>
       <c r="D12" t="n">
-        <v>141.6000061035156</v>
+        <v>156.9199981689453</v>
       </c>
       <c r="E12" t="n">
-        <v>142.6000061035156</v>
+        <v>157.6199951171875</v>
       </c>
       <c r="F12" t="n">
-        <v>50049200</v>
+        <v>39021100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45852</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>146.2400054931641</v>
+        <v>154.7200012207031</v>
       </c>
       <c r="C13" t="n">
-        <v>147.5800018310547</v>
+        <v>156.2299957275391</v>
       </c>
       <c r="D13" t="n">
-        <v>141.8999938964844</v>
+        <v>149.3399963378906</v>
       </c>
       <c r="E13" t="n">
-        <v>145.0899963378906</v>
+        <v>156.1999969482422</v>
       </c>
       <c r="F13" t="n">
-        <v>44718600</v>
+        <v>49028000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45853</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>155.6100006103516</v>
+        <v>158.6499938964844</v>
       </c>
       <c r="C14" t="n">
-        <v>158.6799926757812</v>
+        <v>159.4499969482422</v>
       </c>
       <c r="D14" t="n">
-        <v>153.5599975585938</v>
+        <v>156</v>
       </c>
       <c r="E14" t="n">
-        <v>153.75</v>
+        <v>156.3200073242188</v>
       </c>
       <c r="F14" t="n">
-        <v>93370100</v>
+        <v>41510900</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>160.0800018310547</v>
+        <v>162.1199951171875</v>
       </c>
       <c r="C15" t="n">
-        <v>160.3600006103516</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="D15" t="n">
-        <v>152.8500061035156</v>
+        <v>158.3600006103516</v>
       </c>
       <c r="E15" t="n">
-        <v>155.3099975585938</v>
+        <v>159.1199951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>59492800</v>
+        <v>48440100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>160.4100036621094</v>
+        <v>166.4700012207031</v>
       </c>
       <c r="C16" t="n">
-        <v>161.9600067138672</v>
+        <v>167.1799926757812</v>
       </c>
       <c r="D16" t="n">
-        <v>158.6799926757812</v>
+        <v>162.3600006103516</v>
       </c>
       <c r="E16" t="n">
-        <v>161.8099975585938</v>
+        <v>163.5099945068359</v>
       </c>
       <c r="F16" t="n">
-        <v>50605100</v>
+        <v>53432300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45856</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>156.9900054931641</v>
+        <v>173.6600036621094</v>
       </c>
       <c r="C17" t="n">
-        <v>160.8300018310547</v>
+        <v>174.6999969482422</v>
       </c>
       <c r="D17" t="n">
-        <v>155.8099975585938</v>
+        <v>168.6699981689453</v>
       </c>
       <c r="E17" t="n">
-        <v>159.5899963378906</v>
+        <v>169.0800018310547</v>
       </c>
       <c r="F17" t="n">
-        <v>48859800</v>
+        <v>68267800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>157</v>
+        <v>177.4400024414062</v>
       </c>
       <c r="C18" t="n">
-        <v>160.3399963378906</v>
+        <v>182.3099975585938</v>
       </c>
       <c r="D18" t="n">
-        <v>156.9199981689453</v>
+        <v>174.6799926757812</v>
       </c>
       <c r="E18" t="n">
-        <v>157.6199951171875</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="F18" t="n">
-        <v>39021100</v>
+        <v>108154800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45860</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>154.7200012207031</v>
+        <v>179.5099945068359</v>
       </c>
       <c r="C19" t="n">
-        <v>156.2299957275391</v>
+        <v>180.3699951171875</v>
       </c>
       <c r="D19" t="n">
-        <v>149.3399963378906</v>
+        <v>173.8000030517578</v>
       </c>
       <c r="E19" t="n">
-        <v>156.1999969482422</v>
+        <v>175.6100006103516</v>
       </c>
       <c r="F19" t="n">
-        <v>49028000</v>
+        <v>64820300</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45861</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>158.6499938964844</v>
+        <v>176.3099975585938</v>
       </c>
       <c r="C20" t="n">
-        <v>159.4499969482422</v>
+        <v>182.5</v>
       </c>
       <c r="D20" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E20" t="n">
-        <v>156.3200073242188</v>
+        <v>182.0200042724609</v>
       </c>
       <c r="F20" t="n">
-        <v>41510900</v>
+        <v>71765300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45862</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>162.1199951171875</v>
+        <v>171.6999969482422</v>
       </c>
       <c r="C21" t="n">
-        <v>163.9299926757812</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="D21" t="n">
-        <v>158.3600006103516</v>
+        <v>166.8200073242188</v>
       </c>
       <c r="E21" t="n">
-        <v>159.1199951171875</v>
+        <v>170.1600036621094</v>
       </c>
       <c r="F21" t="n">
-        <v>48440100</v>
+        <v>75396100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>166.4700012207031</v>
+        <v>176.7799987792969</v>
       </c>
       <c r="C22" t="n">
-        <v>167.1799926757812</v>
+        <v>177.8600006103516</v>
       </c>
       <c r="D22" t="n">
-        <v>162.3600006103516</v>
+        <v>173.5599975585938</v>
       </c>
       <c r="E22" t="n">
-        <v>163.5099945068359</v>
+        <v>174.6100006103516</v>
       </c>
       <c r="F22" t="n">
-        <v>53432300</v>
+        <v>52951000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45866</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>173.6600036621094</v>
+        <v>174.3099975585938</v>
       </c>
       <c r="C23" t="n">
-        <v>174.6999969482422</v>
+        <v>177.9900054931641</v>
       </c>
       <c r="D23" t="n">
-        <v>168.6699981689453</v>
+        <v>171.8000030517578</v>
       </c>
       <c r="E23" t="n">
-        <v>169.0800018310547</v>
+        <v>177.5700073242188</v>
       </c>
       <c r="F23" t="n">
-        <v>68267800</v>
+        <v>88808500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45867</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>177.4400024414062</v>
+        <v>163.1199951171875</v>
       </c>
       <c r="C24" t="n">
-        <v>182.3099975585938</v>
+        <v>166.1799926757812</v>
       </c>
       <c r="D24" t="n">
-        <v>174.6799926757812</v>
+        <v>157.8000030517578</v>
       </c>
       <c r="E24" t="n">
-        <v>175.2100067138672</v>
+        <v>165.0500030517578</v>
       </c>
       <c r="F24" t="n">
-        <v>108154800</v>
+        <v>133641800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45868</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>179.5099945068359</v>
+        <v>172.3999938964844</v>
       </c>
       <c r="C25" t="n">
-        <v>180.3699951171875</v>
+        <v>175.75</v>
       </c>
       <c r="D25" t="n">
-        <v>173.8000030517578</v>
+        <v>166.6999969482422</v>
       </c>
       <c r="E25" t="n">
-        <v>175.6100006103516</v>
+        <v>166.8399963378906</v>
       </c>
       <c r="F25" t="n">
-        <v>64820300</v>
+        <v>95448300</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45869</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>176.3099975585938</v>
+        <v>172.7599945068359</v>
       </c>
       <c r="C26" t="n">
-        <v>182.5</v>
+        <v>176.4799957275391</v>
       </c>
       <c r="D26" t="n">
-        <v>173</v>
+        <v>170.5200042724609</v>
       </c>
       <c r="E26" t="n">
-        <v>182.0200042724609</v>
+        <v>174.0399932861328</v>
       </c>
       <c r="F26" t="n">
-        <v>71765300</v>
+        <v>68866700</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45870</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>171.6999969482422</v>
+        <v>172.2799987792969</v>
       </c>
       <c r="C27" t="n">
-        <v>174.3999938964844</v>
+        <v>178.8200073242188</v>
       </c>
       <c r="D27" t="n">
-        <v>166.8200073242188</v>
+        <v>169.3800048828125</v>
       </c>
       <c r="E27" t="n">
-        <v>170.1600036621094</v>
+        <v>170.0399932861328</v>
       </c>
       <c r="F27" t="n">
-        <v>75396100</v>
+        <v>70651000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45873</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>176.7799987792969</v>
+        <v>174.9499969482422</v>
       </c>
       <c r="C28" t="n">
-        <v>177.8600006103516</v>
+        <v>175.1600036621094</v>
       </c>
       <c r="D28" t="n">
-        <v>173.5599975585938</v>
+        <v>168.5</v>
       </c>
       <c r="E28" t="n">
-        <v>174.6100006103516</v>
+        <v>173.3200073242188</v>
       </c>
       <c r="F28" t="n">
-        <v>52951000</v>
+        <v>52243500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45874</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>174.3099975585938</v>
+        <v>184.4199981689453</v>
       </c>
       <c r="C29" t="n">
-        <v>177.9900054931641</v>
+        <v>186.6499938964844</v>
       </c>
       <c r="D29" t="n">
-        <v>171.8000030517578</v>
+        <v>179.3800048828125</v>
       </c>
       <c r="E29" t="n">
-        <v>177.5700073242188</v>
+        <v>179.9100036621094</v>
       </c>
       <c r="F29" t="n">
-        <v>88808500</v>
+        <v>108305100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>163.1199951171875</v>
+        <v>180.9499969482422</v>
       </c>
       <c r="C30" t="n">
-        <v>166.1799926757812</v>
+        <v>185.4400024414062</v>
       </c>
       <c r="D30" t="n">
-        <v>157.8000030517578</v>
+        <v>179.5599975585938</v>
       </c>
       <c r="E30" t="n">
-        <v>165.0500030517578</v>
+        <v>179.8300018310547</v>
       </c>
       <c r="F30" t="n">
-        <v>133641800</v>
+        <v>66308800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>172.3999938964844</v>
+        <v>177.5099945068359</v>
       </c>
       <c r="C31" t="n">
-        <v>175.75</v>
+        <v>180.1399993896484</v>
       </c>
       <c r="D31" t="n">
-        <v>166.6999969482422</v>
+        <v>176.25</v>
       </c>
       <c r="E31" t="n">
-        <v>166.8399963378906</v>
+        <v>180.0599975585938</v>
       </c>
       <c r="F31" t="n">
-        <v>95448300</v>
+        <v>51543100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>172.7599945068359</v>
+        <v>176.1399993896484</v>
       </c>
       <c r="C32" t="n">
-        <v>176.4799957275391</v>
+        <v>178.8000030517578</v>
       </c>
       <c r="D32" t="n">
-        <v>170.5200042724609</v>
+        <v>174.3600006103516</v>
       </c>
       <c r="E32" t="n">
-        <v>174.0399932861328</v>
+        <v>176.7599945068359</v>
       </c>
       <c r="F32" t="n">
-        <v>68866700</v>
+        <v>35937500</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>172.2799987792969</v>
+        <v>166.5500030517578</v>
       </c>
       <c r="C33" t="n">
-        <v>178.8200073242188</v>
+        <v>173.1699981689453</v>
       </c>
       <c r="D33" t="n">
-        <v>169.3800048828125</v>
+        <v>166.1000061035156</v>
       </c>
       <c r="E33" t="n">
-        <v>170.0399932861328</v>
+        <v>173.1000061035156</v>
       </c>
       <c r="F33" t="n">
-        <v>70651000</v>
+        <v>64455000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45881</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>174.9499969482422</v>
+        <v>165.1999969482422</v>
       </c>
       <c r="C34" t="n">
-        <v>175.1600036621094</v>
+        <v>166.6499938964844</v>
       </c>
       <c r="D34" t="n">
-        <v>168.5</v>
+        <v>158.25</v>
       </c>
       <c r="E34" t="n">
-        <v>173.3200073242188</v>
+        <v>164.1000061035156</v>
       </c>
       <c r="F34" t="n">
-        <v>52243500</v>
+        <v>60233200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45882</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>184.4199981689453</v>
+        <v>163.7100067138672</v>
       </c>
       <c r="C35" t="n">
-        <v>186.6499938964844</v>
+        <v>165.8800048828125</v>
       </c>
       <c r="D35" t="n">
-        <v>179.3800048828125</v>
+        <v>162.2599945068359</v>
       </c>
       <c r="E35" t="n">
-        <v>179.9100036621094</v>
+        <v>165.8600006103516</v>
       </c>
       <c r="F35" t="n">
-        <v>108305100</v>
+        <v>37880500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>180.9499969482422</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="C36" t="n">
-        <v>185.4400024414062</v>
+        <v>168.5299987792969</v>
       </c>
       <c r="D36" t="n">
-        <v>179.5599975585938</v>
+        <v>161.8000030517578</v>
       </c>
       <c r="E36" t="n">
-        <v>179.8300018310547</v>
+        <v>162.1699981689453</v>
       </c>
       <c r="F36" t="n">
-        <v>66308800</v>
+        <v>43998600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>177.5099945068359</v>
+        <v>163.3600006103516</v>
       </c>
       <c r="C37" t="n">
-        <v>180.1399993896484</v>
+        <v>165.5899963378906</v>
       </c>
       <c r="D37" t="n">
-        <v>176.25</v>
+        <v>161.7200012207031</v>
       </c>
       <c r="E37" t="n">
-        <v>180.0599975585938</v>
+        <v>165.5500030517578</v>
       </c>
       <c r="F37" t="n">
-        <v>51543100</v>
+        <v>36134700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>176.1399993896484</v>
+        <v>166.6199951171875</v>
       </c>
       <c r="C38" t="n">
-        <v>178.8000030517578</v>
+        <v>169.7700042724609</v>
       </c>
       <c r="D38" t="n">
-        <v>174.3600006103516</v>
+        <v>164.9100036621094</v>
       </c>
       <c r="E38" t="n">
-        <v>176.7599945068359</v>
+        <v>168.6499938964844</v>
       </c>
       <c r="F38" t="n">
-        <v>35937500</v>
+        <v>52138600</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>166.5500030517578</v>
+        <v>167.1300048828125</v>
       </c>
       <c r="C39" t="n">
-        <v>173.1699981689453</v>
+        <v>167.6799926757812</v>
       </c>
       <c r="D39" t="n">
-        <v>166.1000061035156</v>
+        <v>164.6499938964844</v>
       </c>
       <c r="E39" t="n">
-        <v>173.1000061035156</v>
+        <v>166.0399932861328</v>
       </c>
       <c r="F39" t="n">
-        <v>64455000</v>
+        <v>37031000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>165.1999969482422</v>
+        <v>168.5800018310547</v>
       </c>
       <c r="C40" t="n">
+        <v>170.9900054931641</v>
+      </c>
+      <c r="D40" t="n">
         <v>166.6499938964844</v>
       </c>
-      <c r="D40" t="n">
-        <v>158.25</v>
-      </c>
       <c r="E40" t="n">
-        <v>164.1000061035156</v>
+        <v>168.5</v>
       </c>
       <c r="F40" t="n">
-        <v>60233200</v>
+        <v>36285200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45890</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>163.7100067138672</v>
+        <v>162.6300048828125</v>
       </c>
       <c r="C41" t="n">
-        <v>165.8800048828125</v>
+        <v>168.5700073242188</v>
       </c>
       <c r="D41" t="n">
-        <v>162.2599945068359</v>
+        <v>161.8999938964844</v>
       </c>
       <c r="E41" t="n">
-        <v>165.8600006103516</v>
+        <v>166.8099975585938</v>
       </c>
       <c r="F41" t="n">
-        <v>37880500</v>
+        <v>37516800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45902</v>
       </c>
       <c r="B42" t="n">
-        <v>167.7599945068359</v>
+        <v>162.3200073242188</v>
       </c>
       <c r="C42" t="n">
-        <v>168.5299987792969</v>
+        <v>162.3899993896484</v>
       </c>
       <c r="D42" t="n">
-        <v>161.8000030517578</v>
+        <v>156.6199951171875</v>
       </c>
       <c r="E42" t="n">
-        <v>162.1699981689453</v>
+        <v>158.4199981689453</v>
       </c>
       <c r="F42" t="n">
-        <v>43998600</v>
+        <v>38656100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45894</v>
+        <v>45903</v>
       </c>
       <c r="B43" t="n">
-        <v>163.3600006103516</v>
+        <v>162.1300048828125</v>
       </c>
       <c r="C43" t="n">
-        <v>165.5899963378906</v>
+        <v>164.75</v>
       </c>
       <c r="D43" t="n">
-        <v>161.7200012207031</v>
+        <v>160.5800018310547</v>
       </c>
       <c r="E43" t="n">
-        <v>165.5500030517578</v>
+        <v>161.8099975585938</v>
       </c>
       <c r="F43" t="n">
-        <v>36134700</v>
+        <v>30752800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="B44" t="n">
-        <v>166.6199951171875</v>
+        <v>161.7899932861328</v>
       </c>
       <c r="C44" t="n">
-        <v>169.7700042724609</v>
+        <v>162.0500030517578</v>
       </c>
       <c r="D44" t="n">
-        <v>164.9100036621094</v>
+        <v>157.7899932861328</v>
       </c>
       <c r="E44" t="n">
-        <v>168.6499938964844</v>
+        <v>159.9400024414062</v>
       </c>
       <c r="F44" t="n">
-        <v>52138600</v>
+        <v>32103500</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="B45" t="n">
-        <v>167.1300048828125</v>
+        <v>151.1399993896484</v>
       </c>
       <c r="C45" t="n">
-        <v>167.6799926757812</v>
+        <v>157.1399993896484</v>
       </c>
       <c r="D45" t="n">
-        <v>164.6499938964844</v>
+        <v>150.1799926757812</v>
       </c>
       <c r="E45" t="n">
-        <v>166.0399932861328</v>
+        <v>157.1199951171875</v>
       </c>
       <c r="F45" t="n">
-        <v>37031000</v>
+        <v>78256000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45897</v>
+        <v>45908</v>
       </c>
       <c r="B46" t="n">
-        <v>168.5800018310547</v>
+        <v>151.4100036621094</v>
       </c>
       <c r="C46" t="n">
-        <v>170.9900054931641</v>
+        <v>152.6399993896484</v>
       </c>
       <c r="D46" t="n">
-        <v>166.6499938964844</v>
+        <v>149.2200012207031</v>
       </c>
       <c r="E46" t="n">
-        <v>168.5</v>
+        <v>151.8000030517578</v>
       </c>
       <c r="F46" t="n">
-        <v>36285200</v>
+        <v>41849000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="B47" t="n">
-        <v>162.6300048828125</v>
+        <v>155.8200073242188</v>
       </c>
       <c r="C47" t="n">
-        <v>168.5700073242188</v>
+        <v>156.6600036621094</v>
       </c>
       <c r="D47" t="n">
-        <v>161.8999938964844</v>
+        <v>151.9299926757812</v>
       </c>
       <c r="E47" t="n">
-        <v>166.8099975585938</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="F47" t="n">
-        <v>37516800</v>
+        <v>42802500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B48" t="n">
-        <v>162.3200073242188</v>
+        <v>159.5399932861328</v>
       </c>
       <c r="C48" t="n">
-        <v>162.3899993896484</v>
+        <v>164.5299987792969</v>
       </c>
       <c r="D48" t="n">
-        <v>156.6199951171875</v>
+        <v>158</v>
       </c>
       <c r="E48" t="n">
-        <v>158.4199981689453</v>
+        <v>163.5399932861328</v>
       </c>
       <c r="F48" t="n">
-        <v>38656100</v>
+        <v>52465300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B49" t="n">
-        <v>162.1300048828125</v>
+        <v>155.6699981689453</v>
       </c>
       <c r="C49" t="n">
-        <v>164.75</v>
+        <v>160.2100067138672</v>
       </c>
       <c r="D49" t="n">
-        <v>160.5800018310547</v>
+        <v>154.9900054931641</v>
       </c>
       <c r="E49" t="n">
-        <v>161.8099975585938</v>
+        <v>158.6199951171875</v>
       </c>
       <c r="F49" t="n">
-        <v>30752800</v>
+        <v>48817700</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B50" t="n">
-        <v>161.7899932861328</v>
+        <v>158.5700073242188</v>
       </c>
       <c r="C50" t="n">
-        <v>162.0500030517578</v>
+        <v>160.4100036621094</v>
       </c>
       <c r="D50" t="n">
-        <v>157.7899932861328</v>
+        <v>154.9199981689453</v>
       </c>
       <c r="E50" t="n">
-        <v>159.9400024414062</v>
+        <v>157</v>
       </c>
       <c r="F50" t="n">
-        <v>32103500</v>
+        <v>42232800</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B51" t="n">
-        <v>151.1399993896484</v>
+        <v>161.1600036621094</v>
       </c>
       <c r="C51" t="n">
-        <v>157.1399993896484</v>
+        <v>162.3000030517578</v>
       </c>
       <c r="D51" t="n">
-        <v>150.1799926757812</v>
+        <v>157.6000061035156</v>
       </c>
       <c r="E51" t="n">
-        <v>157.1199951171875</v>
+        <v>160.0099945068359</v>
       </c>
       <c r="F51" t="n">
-        <v>78256000</v>
+        <v>36808700</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B52" t="n">
-        <v>151.4100036621094</v>
+        <v>160.4600067138672</v>
       </c>
       <c r="C52" t="n">
-        <v>152.6399993896484</v>
+        <v>161.9499969482422</v>
       </c>
       <c r="D52" t="n">
-        <v>149.2200012207031</v>
+        <v>159.2200012207031</v>
       </c>
       <c r="E52" t="n">
-        <v>151.8000030517578</v>
+        <v>161.3699951171875</v>
       </c>
       <c r="F52" t="n">
-        <v>41849000</v>
+        <v>27946500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B53" t="n">
-        <v>155.8200073242188</v>
+        <v>159.1600036621094</v>
       </c>
       <c r="C53" t="n">
-        <v>156.6600036621094</v>
+        <v>161.6300048828125</v>
       </c>
       <c r="D53" t="n">
-        <v>151.9299926757812</v>
+        <v>155.7599945068359</v>
       </c>
       <c r="E53" t="n">
-        <v>151.9900054931641</v>
+        <v>159.2799987792969</v>
       </c>
       <c r="F53" t="n">
-        <v>42802500</v>
+        <v>41823800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B54" t="n">
-        <v>159.5399932861328</v>
+        <v>157.9199981689453</v>
       </c>
       <c r="C54" t="n">
-        <v>164.5299987792969</v>
+        <v>158.7700042724609</v>
       </c>
       <c r="D54" t="n">
-        <v>158</v>
+        <v>149.8500061035156</v>
       </c>
       <c r="E54" t="n">
-        <v>163.5399932861328</v>
+        <v>150.9600067138672</v>
       </c>
       <c r="F54" t="n">
-        <v>52465300</v>
+        <v>84549500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B55" t="n">
-        <v>155.6699981689453</v>
+        <v>157.3899993896484</v>
       </c>
       <c r="C55" t="n">
-        <v>160.2100067138672</v>
+        <v>159.8399963378906</v>
       </c>
       <c r="D55" t="n">
-        <v>154.9900054931641</v>
+        <v>155.8999938964844</v>
       </c>
       <c r="E55" t="n">
-        <v>158.6199951171875</v>
+        <v>157.3800048828125</v>
       </c>
       <c r="F55" t="n">
-        <v>48817700</v>
+        <v>55448100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B56" t="n">
-        <v>158.5700073242188</v>
+        <v>159.7899932861328</v>
       </c>
       <c r="C56" t="n">
-        <v>160.4100036621094</v>
+        <v>162.6799926757812</v>
       </c>
       <c r="D56" t="n">
-        <v>154.9199981689453</v>
+        <v>157.4199981689453</v>
       </c>
       <c r="E56" t="n">
-        <v>157</v>
+        <v>157.4199981689453</v>
       </c>
       <c r="F56" t="n">
-        <v>42232800</v>
+        <v>46505500</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B57" t="n">
-        <v>161.1600036621094</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="C57" t="n">
-        <v>162.3000030517578</v>
+        <v>163.3899993896484</v>
       </c>
       <c r="D57" t="n">
-        <v>157.6000061035156</v>
+        <v>159.2100067138672</v>
       </c>
       <c r="E57" t="n">
-        <v>160.0099945068359</v>
+        <v>160.5200042724609</v>
       </c>
       <c r="F57" t="n">
-        <v>36808700</v>
+        <v>39448300</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B58" t="n">
-        <v>160.4600067138672</v>
+        <v>160.8800048828125</v>
       </c>
       <c r="C58" t="n">
-        <v>161.9499969482422</v>
+        <v>165.1000061035156</v>
       </c>
       <c r="D58" t="n">
-        <v>159.2200012207031</v>
+        <v>158.4299926757812</v>
       </c>
       <c r="E58" t="n">
-        <v>161.3699951171875</v>
+        <v>162.9799957275391</v>
       </c>
       <c r="F58" t="n">
-        <v>27946500</v>
+        <v>38464100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B59" t="n">
-        <v>159.1600036621094</v>
+        <v>161.2700042724609</v>
       </c>
       <c r="C59" t="n">
         <v>161.6300048828125</v>
       </c>
       <c r="D59" t="n">
-        <v>155.7599945068359</v>
+        <v>154.7799987792969</v>
       </c>
       <c r="E59" t="n">
-        <v>159.2799987792969</v>
+        <v>157.1399993896484</v>
       </c>
       <c r="F59" t="n">
-        <v>41823800</v>
+        <v>36809900</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B60" t="n">
-        <v>157.9199981689453</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="C60" t="n">
-        <v>158.7700042724609</v>
+        <v>162.1100006103516</v>
       </c>
       <c r="D60" t="n">
-        <v>149.8500061035156</v>
+        <v>157.0500030517578</v>
       </c>
       <c r="E60" t="n">
-        <v>150.9600067138672</v>
+        <v>160.5200042724609</v>
       </c>
       <c r="F60" t="n">
-        <v>84549500</v>
+        <v>30316900</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>157.3899993896484</v>
+        <v>161.3600006103516</v>
       </c>
       <c r="C61" t="n">
-        <v>159.8399963378906</v>
+        <v>164.3000030517578</v>
       </c>
       <c r="D61" t="n">
-        <v>155.8999938964844</v>
+        <v>159.8999938964844</v>
       </c>
       <c r="E61" t="n">
-        <v>157.3800048828125</v>
+        <v>160.1199951171875</v>
       </c>
       <c r="F61" t="n">
-        <v>55448100</v>
+        <v>39828800</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45922</v>
+        <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>159.7899932861328</v>
+        <v>161.7899932861328</v>
       </c>
       <c r="C62" t="n">
-        <v>162.6799926757812</v>
+        <v>162.2799987792969</v>
       </c>
       <c r="D62" t="n">
-        <v>157.4199981689453</v>
+        <v>159.3300018310547</v>
       </c>
       <c r="E62" t="n">
-        <v>157.4199981689453</v>
+        <v>160.7899932861328</v>
       </c>
       <c r="F62" t="n">
-        <v>46505500</v>
+        <v>29669300</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>160.8999938964844</v>
+        <v>164.0099945068359</v>
       </c>
       <c r="C63" t="n">
-        <v>163.3899993896484</v>
+        <v>164.1799926757812</v>
       </c>
       <c r="D63" t="n">
-        <v>159.2100067138672</v>
+        <v>160.4900054931641</v>
       </c>
       <c r="E63" t="n">
-        <v>160.5200042724609</v>
+        <v>160.9299926757812</v>
       </c>
       <c r="F63" t="n">
-        <v>39448300</v>
+        <v>39895200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>160.8800048828125</v>
+        <v>169.7299957275391</v>
       </c>
       <c r="C64" t="n">
-        <v>165.1000061035156</v>
+        <v>171.0599975585938</v>
       </c>
       <c r="D64" t="n">
-        <v>158.4299926757812</v>
+        <v>166.1199951171875</v>
       </c>
       <c r="E64" t="n">
-        <v>162.9799957275391</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="F64" t="n">
-        <v>38464100</v>
+        <v>55475200</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>161.2700042724609</v>
+        <v>164.6699981689453</v>
       </c>
       <c r="C65" t="n">
-        <v>161.6300048828125</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="D65" t="n">
-        <v>154.7799987792969</v>
+        <v>163.1399993896484</v>
       </c>
       <c r="E65" t="n">
-        <v>157.1399993896484</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="F65" t="n">
-        <v>36809900</v>
+        <v>42699100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="B66" t="n">
-        <v>159.4600067138672</v>
+        <v>203.7100067138672</v>
       </c>
       <c r="C66" t="n">
-        <v>162.1100006103516</v>
+        <v>226.7100067138672</v>
       </c>
       <c r="D66" t="n">
-        <v>157.0500030517578</v>
+        <v>203.0099945068359</v>
       </c>
       <c r="E66" t="n">
-        <v>160.5200042724609</v>
+        <v>226.4499969482422</v>
       </c>
       <c r="F66" t="n">
-        <v>30316900</v>
+        <v>248859600</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="B67" t="n">
-        <v>161.3600006103516</v>
+        <v>211.5099945068359</v>
       </c>
       <c r="C67" t="n">
-        <v>164.3000030517578</v>
+        <v>218.8999938964844</v>
       </c>
       <c r="D67" t="n">
-        <v>159.8999938964844</v>
+        <v>209.2799987792969</v>
       </c>
       <c r="E67" t="n">
-        <v>160.1199951171875</v>
+        <v>214.8500061035156</v>
       </c>
       <c r="F67" t="n">
-        <v>39828800</v>
+        <v>115748100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="B68" t="n">
-        <v>161.7899932861328</v>
+        <v>235.5599975585938</v>
       </c>
       <c r="C68" t="n">
-        <v>162.2799987792969</v>
+        <v>235.8699951171875</v>
       </c>
       <c r="D68" t="n">
-        <v>159.3300018310547</v>
+        <v>210.6999969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>160.7899932861328</v>
+        <v>212.9499969482422</v>
       </c>
       <c r="F68" t="n">
-        <v>29669300</v>
+        <v>159983500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45931</v>
+        <v>45939</v>
       </c>
       <c r="B69" t="n">
-        <v>164.0099945068359</v>
+        <v>232.8899993896484</v>
       </c>
       <c r="C69" t="n">
-        <v>164.1799926757812</v>
+        <v>240.1000061035156</v>
       </c>
       <c r="D69" t="n">
-        <v>160.4900054931641</v>
+        <v>229.5299987792969</v>
       </c>
       <c r="E69" t="n">
-        <v>160.9299926757812</v>
+        <v>236.3000030517578</v>
       </c>
       <c r="F69" t="n">
-        <v>39895200</v>
+        <v>94290700</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45932</v>
+        <v>45940</v>
       </c>
       <c r="B70" t="n">
-        <v>169.7299957275391</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C70" t="n">
-        <v>171.0599975585938</v>
+        <v>234.2200012207031</v>
       </c>
       <c r="D70" t="n">
-        <v>166.1199951171875</v>
+        <v>213.1999969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>168.6799926757812</v>
+        <v>232.7700042724609</v>
       </c>
       <c r="F70" t="n">
-        <v>55475200</v>
+        <v>118656600</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45933</v>
+        <v>45943</v>
       </c>
       <c r="B71" t="n">
-        <v>164.6699981689453</v>
+        <v>216.4199981689453</v>
       </c>
       <c r="C71" t="n">
-        <v>170.6799926757812</v>
+        <v>224.1900024414062</v>
       </c>
       <c r="D71" t="n">
-        <v>163.1399993896484</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="E71" t="n">
-        <v>170.6799926757812</v>
+        <v>220.1999969482422</v>
       </c>
       <c r="F71" t="n">
-        <v>42699100</v>
+        <v>63104000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="B72" t="n">
-        <v>203.7100067138672</v>
+        <v>218.0899963378906</v>
       </c>
       <c r="C72" t="n">
-        <v>226.7100067138672</v>
+        <v>224.9799957275391</v>
       </c>
       <c r="D72" t="n">
-        <v>203.0099945068359</v>
+        <v>215.8999938964844</v>
       </c>
       <c r="E72" t="n">
-        <v>226.4499969482422</v>
+        <v>219.1999969482422</v>
       </c>
       <c r="F72" t="n">
-        <v>248859600</v>
+        <v>71216300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45937</v>
+        <v>45945</v>
       </c>
       <c r="B73" t="n">
-        <v>211.5099945068359</v>
+        <v>238.6000061035156</v>
       </c>
       <c r="C73" t="n">
-        <v>218.8999938964844</v>
+        <v>239.2400054931641</v>
       </c>
       <c r="D73" t="n">
-        <v>209.2799987792969</v>
+        <v>220.7599945068359</v>
       </c>
       <c r="E73" t="n">
-        <v>214.8500061035156</v>
+        <v>222.7100067138672</v>
       </c>
       <c r="F73" t="n">
-        <v>115748100</v>
+        <v>108481000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45938</v>
+        <v>45946</v>
       </c>
       <c r="B74" t="n">
-        <v>235.5599975585938</v>
+        <v>234.5599975585938</v>
       </c>
       <c r="C74" t="n">
-        <v>235.8699951171875</v>
+        <v>241.1999969482422</v>
       </c>
       <c r="D74" t="n">
-        <v>210.6999969482422</v>
+        <v>232.2400054931641</v>
       </c>
       <c r="E74" t="n">
-        <v>212.9499969482422</v>
+        <v>236.2899932861328</v>
       </c>
       <c r="F74" t="n">
-        <v>159983500</v>
+        <v>69726400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="B75" t="n">
-        <v>232.8899993896484</v>
+        <v>233.0800018310547</v>
       </c>
       <c r="C75" t="n">
-        <v>240.1000061035156</v>
+        <v>235.3800048828125</v>
       </c>
       <c r="D75" t="n">
-        <v>229.5299987792969</v>
+        <v>227.9100036621094</v>
       </c>
       <c r="E75" t="n">
-        <v>236.3000030517578</v>
+        <v>233.2599945068359</v>
       </c>
       <c r="F75" t="n">
-        <v>94290700</v>
+        <v>55804200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="B76" t="n">
-        <v>214.8999938964844</v>
+        <v>240.5599975585938</v>
       </c>
       <c r="C76" t="n">
-        <v>234.2200012207031</v>
+        <v>242.8800048828125</v>
       </c>
       <c r="D76" t="n">
-        <v>213.1999969482422</v>
+        <v>234.3999938964844</v>
       </c>
       <c r="E76" t="n">
-        <v>232.7700042724609</v>
+        <v>236.4700012207031</v>
       </c>
       <c r="F76" t="n">
-        <v>118656600</v>
+        <v>56741700</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="B77" t="n">
-        <v>216.4199981689453</v>
+        <v>238.0299987792969</v>
       </c>
       <c r="C77" t="n">
-        <v>224.1900024414062</v>
+        <v>242.2599945068359</v>
       </c>
       <c r="D77" t="n">
-        <v>214.8999938964844</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="E77" t="n">
-        <v>220.1999969482422</v>
+        <v>239.3899993896484</v>
       </c>
       <c r="F77" t="n">
-        <v>63104000</v>
+        <v>47122400</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45944</v>
+        <v>45952</v>
       </c>
       <c r="B78" t="n">
-        <v>218.0899963378906</v>
+        <v>230.2299957275391</v>
       </c>
       <c r="C78" t="n">
-        <v>224.9799957275391</v>
+        <v>240.1300048828125</v>
       </c>
       <c r="D78" t="n">
-        <v>215.8999938964844</v>
+        <v>224.8800048828125</v>
       </c>
       <c r="E78" t="n">
-        <v>219.1999969482422</v>
+        <v>236.8500061035156</v>
       </c>
       <c r="F78" t="n">
-        <v>71216300</v>
+        <v>59668800</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="B79" t="n">
-        <v>238.6000061035156</v>
+        <v>234.9900054931641</v>
       </c>
       <c r="C79" t="n">
-        <v>239.2400054931641</v>
+        <v>235.8999938964844</v>
       </c>
       <c r="D79" t="n">
-        <v>220.7599945068359</v>
+        <v>228.5399932861328</v>
       </c>
       <c r="E79" t="n">
-        <v>222.7100067138672</v>
+        <v>230.1600036621094</v>
       </c>
       <c r="F79" t="n">
-        <v>108481000</v>
+        <v>39024400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45946</v>
+        <v>45954</v>
       </c>
       <c r="B80" t="n">
-        <v>234.5599975585938</v>
+        <v>252.9199981689453</v>
       </c>
       <c r="C80" t="n">
-        <v>241.1999969482422</v>
+        <v>253.3899993896484</v>
       </c>
       <c r="D80" t="n">
-        <v>232.2400054931641</v>
+        <v>241.9499969482422</v>
       </c>
       <c r="E80" t="n">
-        <v>236.2899932861328</v>
+        <v>243.3600006103516</v>
       </c>
       <c r="F80" t="n">
-        <v>69726400</v>
+        <v>71221100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45947</v>
+        <v>45957</v>
       </c>
       <c r="B81" t="n">
-        <v>233.0800018310547</v>
+        <v>259.6700134277344</v>
       </c>
       <c r="C81" t="n">
-        <v>235.3800048828125</v>
+        <v>260.4200134277344</v>
       </c>
       <c r="D81" t="n">
-        <v>227.9100036621094</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="E81" t="n">
-        <v>233.2599945068359</v>
+        <v>257.8800048828125</v>
       </c>
       <c r="F81" t="n">
-        <v>55804200</v>
+        <v>65613100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="B82" t="n">
-        <v>240.5599975585938</v>
+        <v>258.010009765625</v>
       </c>
       <c r="C82" t="n">
-        <v>242.8800048828125</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="D82" t="n">
-        <v>234.3999938964844</v>
+        <v>257</v>
       </c>
       <c r="E82" t="n">
-        <v>236.4700012207031</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="F82" t="n">
-        <v>56741700</v>
+        <v>47448700</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45951</v>
+        <v>45959</v>
       </c>
       <c r="B83" t="n">
-        <v>238.0299987792969</v>
+        <v>264.3299865722656</v>
       </c>
       <c r="C83" t="n">
-        <v>242.2599945068359</v>
+        <v>267.0799865722656</v>
       </c>
       <c r="D83" t="n">
-        <v>234.0200042724609</v>
+        <v>257.3999938964844</v>
       </c>
       <c r="E83" t="n">
-        <v>239.3899993896484</v>
+        <v>264.1900024414062</v>
       </c>
       <c r="F83" t="n">
-        <v>47122400</v>
+        <v>49335600</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="n">
-        <v>230.2299957275391</v>
+        <v>254.8399963378906</v>
       </c>
       <c r="C84" t="n">
-        <v>240.1300048828125</v>
+        <v>263.8800048828125</v>
       </c>
       <c r="D84" t="n">
-        <v>224.8800048828125</v>
+        <v>252.3099975585938</v>
       </c>
       <c r="E84" t="n">
-        <v>236.8500061035156</v>
+        <v>259.9200134277344</v>
       </c>
       <c r="F84" t="n">
-        <v>59668800</v>
+        <v>45162500</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="B85" t="n">
-        <v>234.9900054931641</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="C85" t="n">
-        <v>235.8999938964844</v>
+        <v>262.1300048828125</v>
       </c>
       <c r="D85" t="n">
-        <v>228.5399932861328</v>
+        <v>253.4100036621094</v>
       </c>
       <c r="E85" t="n">
-        <v>230.1600036621094</v>
+        <v>259.6000061035156</v>
       </c>
       <c r="F85" t="n">
-        <v>39024400</v>
+        <v>34449200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="B86" t="n">
-        <v>252.9199981689453</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="C86" t="n">
-        <v>253.3899993896484</v>
+        <v>260.9100036621094</v>
       </c>
       <c r="D86" t="n">
-        <v>241.9499969482422</v>
+        <v>253.8899993896484</v>
       </c>
       <c r="E86" t="n">
-        <v>243.3600006103516</v>
+        <v>259.3299865722656</v>
       </c>
       <c r="F86" t="n">
-        <v>71221100</v>
+        <v>36351400</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="B87" t="n">
-        <v>259.6700134277344</v>
+        <v>250.0500030517578</v>
       </c>
       <c r="C87" t="n">
-        <v>260.4200134277344</v>
+        <v>257.3800048828125</v>
       </c>
       <c r="D87" t="n">
-        <v>249.8000030517578</v>
+        <v>247.3899993896484</v>
       </c>
       <c r="E87" t="n">
-        <v>257.8800048828125</v>
+        <v>250.3500061035156</v>
       </c>
       <c r="F87" t="n">
-        <v>65613100</v>
+        <v>56491800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="B88" t="n">
-        <v>258.010009765625</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="C88" t="n">
-        <v>264.5799865722656</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="D88" t="n">
-        <v>257</v>
+        <v>242.8099975585938</v>
       </c>
       <c r="E88" t="n">
-        <v>259.1400146484375</v>
+        <v>243.2400054931641</v>
       </c>
       <c r="F88" t="n">
-        <v>47448700</v>
+        <v>67366600</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="B89" t="n">
-        <v>264.3299865722656</v>
+        <v>237.6999969482422</v>
       </c>
       <c r="C89" t="n">
-        <v>267.0799865722656</v>
+        <v>253.5099945068359</v>
       </c>
       <c r="D89" t="n">
-        <v>257.3999938964844</v>
+        <v>235.7400054931641</v>
       </c>
       <c r="E89" t="n">
-        <v>264.1900024414062</v>
+        <v>253.4700012207031</v>
       </c>
       <c r="F89" t="n">
-        <v>49335600</v>
+        <v>66049700</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="B90" t="n">
-        <v>254.8399963378906</v>
+        <v>233.5399932861328</v>
       </c>
       <c r="C90" t="n">
-        <v>263.8800048828125</v>
+        <v>235.8699951171875</v>
       </c>
       <c r="D90" t="n">
-        <v>252.3099975585938</v>
+        <v>224.6399993896484</v>
       </c>
       <c r="E90" t="n">
-        <v>259.9200134277344</v>
+        <v>230.9400024414062</v>
       </c>
       <c r="F90" t="n">
-        <v>45162500</v>
+        <v>52162600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="B91" t="n">
-        <v>256.1199951171875</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="C91" t="n">
-        <v>262.1300048828125</v>
+        <v>248.8999938964844</v>
       </c>
       <c r="D91" t="n">
-        <v>253.4100036621094</v>
+        <v>240.5</v>
       </c>
       <c r="E91" t="n">
-        <v>259.6000061035156</v>
+        <v>242.1399993896484</v>
       </c>
       <c r="F91" t="n">
-        <v>34449200</v>
+        <v>43361600</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B92" t="n">
-        <v>259.6499938964844</v>
+        <v>237.5200042724609</v>
       </c>
       <c r="C92" t="n">
-        <v>260.9100036621094</v>
+        <v>248.4600067138672</v>
       </c>
       <c r="D92" t="n">
-        <v>253.8899993896484</v>
+        <v>234.6399993896484</v>
       </c>
       <c r="E92" t="n">
-        <v>259.3299865722656</v>
+        <v>241.6600036621094</v>
       </c>
       <c r="F92" t="n">
-        <v>36351400</v>
+        <v>61336800</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45965</v>
+        <v>45973</v>
       </c>
       <c r="B93" t="n">
-        <v>250.0500030517578</v>
+        <v>258.8900146484375</v>
       </c>
       <c r="C93" t="n">
-        <v>257.3800048828125</v>
+        <v>263.510009765625</v>
       </c>
       <c r="D93" t="n">
-        <v>247.3899993896484</v>
+        <v>250</v>
       </c>
       <c r="E93" t="n">
-        <v>250.3500061035156</v>
+        <v>253.1300048828125</v>
       </c>
       <c r="F93" t="n">
-        <v>56491800</v>
+        <v>108942000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="B94" t="n">
-        <v>256.3299865722656</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="C94" t="n">
-        <v>259.6499938964844</v>
+        <v>259.6300048828125</v>
       </c>
       <c r="D94" t="n">
-        <v>242.8099975585938</v>
+        <v>246.0599975585938</v>
       </c>
       <c r="E94" t="n">
-        <v>243.2400054931641</v>
+        <v>251.8999938964844</v>
       </c>
       <c r="F94" t="n">
-        <v>67366600</v>
+        <v>63178600</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45967</v>
+        <v>45975</v>
       </c>
       <c r="B95" t="n">
-        <v>237.6999969482422</v>
+        <v>246.8099975585938</v>
       </c>
       <c r="C95" t="n">
-        <v>253.5099945068359</v>
+        <v>253.4400024414062</v>
       </c>
       <c r="D95" t="n">
-        <v>235.7400054931641</v>
+        <v>235.0800018310547</v>
       </c>
       <c r="E95" t="n">
-        <v>253.4700012207031</v>
+        <v>240.1100006103516</v>
       </c>
       <c r="F95" t="n">
-        <v>66049700</v>
+        <v>47655600</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="B96" t="n">
-        <v>233.5399932861328</v>
+        <v>240.5200042724609</v>
       </c>
       <c r="C96" t="n">
-        <v>235.8699951171875</v>
+        <v>248.7700042724609</v>
       </c>
       <c r="D96" t="n">
-        <v>224.6399993896484</v>
+        <v>237.1499938964844</v>
       </c>
       <c r="E96" t="n">
-        <v>230.9400024414062</v>
+        <v>242.75</v>
       </c>
       <c r="F96" t="n">
-        <v>52162600</v>
+        <v>37942200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45971</v>
+        <v>45979</v>
       </c>
       <c r="B97" t="n">
-        <v>243.9799957275391</v>
+        <v>230.2899932861328</v>
       </c>
       <c r="C97" t="n">
-        <v>248.8999938964844</v>
+        <v>238</v>
       </c>
       <c r="D97" t="n">
-        <v>240.5</v>
+        <v>224.7100067138672</v>
       </c>
       <c r="E97" t="n">
-        <v>242.1399993896484</v>
+        <v>236.7799987792969</v>
       </c>
       <c r="F97" t="n">
-        <v>43361600</v>
+        <v>45619900</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45972</v>
+        <v>45980</v>
       </c>
       <c r="B98" t="n">
-        <v>237.5200042724609</v>
+        <v>223.5500030517578</v>
       </c>
       <c r="C98" t="n">
-        <v>248.4600067138672</v>
+        <v>235.2799987792969</v>
       </c>
       <c r="D98" t="n">
-        <v>234.6399993896484</v>
+        <v>219.7100067138672</v>
       </c>
       <c r="E98" t="n">
-        <v>241.6600036621094</v>
+        <v>230.2599945068359</v>
       </c>
       <c r="F98" t="n">
-        <v>61336800</v>
+        <v>52093400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B99" t="n">
-        <v>258.8900146484375</v>
+        <v>206.0200042724609</v>
       </c>
       <c r="C99" t="n">
-        <v>263.510009765625</v>
+        <v>234.25</v>
       </c>
       <c r="D99" t="n">
-        <v>250</v>
+        <v>204.5299987792969</v>
       </c>
       <c r="E99" t="n">
-        <v>253.1300048828125</v>
+        <v>232.6999969482422</v>
       </c>
       <c r="F99" t="n">
-        <v>108942000</v>
+        <v>66342900</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45974</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>247.9600067138672</v>
+        <v>203.7799987792969</v>
       </c>
       <c r="C100" t="n">
-        <v>259.6300048828125</v>
+        <v>208.8300018310547</v>
       </c>
       <c r="D100" t="n">
-        <v>246.0599975585938</v>
+        <v>195</v>
       </c>
       <c r="E100" t="n">
-        <v>251.8999938964844</v>
+        <v>208.8099975585938</v>
       </c>
       <c r="F100" t="n">
-        <v>63178600</v>
+        <v>67421100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>246.8099975585938</v>
+        <v>215.0500030517578</v>
       </c>
       <c r="C101" t="n">
-        <v>253.4400024414062</v>
+        <v>217.1300048828125</v>
       </c>
       <c r="D101" t="n">
-        <v>235.0800018310547</v>
+        <v>205.8500061035156</v>
       </c>
       <c r="E101" t="n">
-        <v>240.1100006103516</v>
+        <v>207.1600036621094</v>
       </c>
       <c r="F101" t="n">
-        <v>47655600</v>
+        <v>46749600</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>240.5200042724609</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="C102" t="n">
-        <v>248.7700042724609</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="D102" t="n">
-        <v>237.1499938964844</v>
+        <v>194.2799987792969</v>
       </c>
       <c r="E102" t="n">
-        <v>242.75</v>
+        <v>201.4799957275391</v>
       </c>
       <c r="F102" t="n">
-        <v>37942200</v>
+        <v>69773500</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>230.2899932861328</v>
+        <v>214.2400054931641</v>
       </c>
       <c r="C103" t="n">
-        <v>238</v>
+        <v>215.5899963378906</v>
       </c>
       <c r="D103" t="n">
-        <v>224.7100067138672</v>
+        <v>207</v>
       </c>
       <c r="E103" t="n">
-        <v>236.7799987792969</v>
+        <v>210.0500030517578</v>
       </c>
       <c r="F103" t="n">
-        <v>45619900</v>
+        <v>43270200</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="B104" t="n">
-        <v>223.5500030517578</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="C104" t="n">
-        <v>235.2799987792969</v>
+        <v>218.3000030517578</v>
       </c>
       <c r="D104" t="n">
-        <v>219.7100067138672</v>
+        <v>214.0200042724609</v>
       </c>
       <c r="E104" t="n">
-        <v>230.2599945068359</v>
+        <v>216.1399993896484</v>
       </c>
       <c r="F104" t="n">
-        <v>52093400</v>
+        <v>18658000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45981</v>
+        <v>45992</v>
       </c>
       <c r="B105" t="n">
-        <v>206.0200042724609</v>
+        <v>219.7599945068359</v>
       </c>
       <c r="C105" t="n">
-        <v>234.25</v>
+        <v>220.9799957275391</v>
       </c>
       <c r="D105" t="n">
-        <v>204.5299987792969</v>
+        <v>213.5</v>
       </c>
       <c r="E105" t="n">
-        <v>232.6999969482422</v>
+        <v>213.8800048828125</v>
       </c>
       <c r="F105" t="n">
-        <v>66342900</v>
+        <v>30768700</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="B106" t="n">
-        <v>203.7799987792969</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="C106" t="n">
-        <v>208.8300018310547</v>
+        <v>225.9799957275391</v>
       </c>
       <c r="D106" t="n">
-        <v>195</v>
+        <v>214.3899993896484</v>
       </c>
       <c r="E106" t="n">
-        <v>208.8099975585938</v>
+        <v>221.7899932861328</v>
       </c>
       <c r="F106" t="n">
-        <v>67421100</v>
+        <v>42002500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="B107" t="n">
-        <v>215.0500030517578</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="C107" t="n">
-        <v>217.1300048828125</v>
+        <v>218.1999969482422</v>
       </c>
       <c r="D107" t="n">
-        <v>205.8500061035156</v>
+        <v>211.7700042724609</v>
       </c>
       <c r="E107" t="n">
-        <v>207.1600036621094</v>
+        <v>216.2599945068359</v>
       </c>
       <c r="F107" t="n">
-        <v>46749600</v>
+        <v>28545200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="B108" t="n">
-        <v>206.1300048828125</v>
+        <v>215.9799957275391</v>
       </c>
       <c r="C108" t="n">
-        <v>206.5800018310547</v>
+        <v>219.1199951171875</v>
       </c>
       <c r="D108" t="n">
-        <v>194.2799987792969</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="E108" t="n">
-        <v>201.4799957275391</v>
+        <v>216.8800048828125</v>
       </c>
       <c r="F108" t="n">
-        <v>69773500</v>
+        <v>24478200</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45987</v>
+        <v>45996</v>
       </c>
       <c r="B109" t="n">
-        <v>214.2400054931641</v>
+        <v>217.9700012207031</v>
       </c>
       <c r="C109" t="n">
-        <v>215.5899963378906</v>
+        <v>223.6399993896484</v>
       </c>
       <c r="D109" t="n">
-        <v>207</v>
+        <v>216.2400054931641</v>
       </c>
       <c r="E109" t="n">
-        <v>210.0500030517578</v>
+        <v>217.1699981689453</v>
       </c>
       <c r="F109" t="n">
-        <v>43270200</v>
+        <v>33292400</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45989</v>
+        <v>45999</v>
       </c>
       <c r="B110" t="n">
-        <v>217.5299987792969</v>
+        <v>221.1100006103516</v>
       </c>
       <c r="C110" t="n">
-        <v>218.3000030517578</v>
+        <v>223.7100067138672</v>
       </c>
       <c r="D110" t="n">
-        <v>214.0200042724609</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="E110" t="n">
-        <v>216.1399993896484</v>
+        <v>219.0899963378906</v>
       </c>
       <c r="F110" t="n">
-        <v>18658000</v>
+        <v>30943200</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="B111" t="n">
-        <v>219.7599945068359</v>
+        <v>221.6199951171875</v>
       </c>
       <c r="C111" t="n">
-        <v>220.9799957275391</v>
+        <v>224.8399963378906</v>
       </c>
       <c r="D111" t="n">
-        <v>213.5</v>
+        <v>217.9100036621094</v>
       </c>
       <c r="E111" t="n">
-        <v>213.8800048828125</v>
+        <v>221.0399932861328</v>
       </c>
       <c r="F111" t="n">
-        <v>30768700</v>
+        <v>25166100</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="B112" t="n">
-        <v>215.2400054931641</v>
+        <v>221.4199981689453</v>
       </c>
       <c r="C112" t="n">
-        <v>225.9799957275391</v>
+        <v>222.6100006103516</v>
       </c>
       <c r="D112" t="n">
-        <v>214.3899993896484</v>
+        <v>218.6699981689453</v>
       </c>
       <c r="E112" t="n">
-        <v>221.7899932861328</v>
+        <v>222</v>
       </c>
       <c r="F112" t="n">
-        <v>42002500</v>
+        <v>23279400</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B113" t="n">
-        <v>217.6000061035156</v>
+        <v>221.4299926757812</v>
       </c>
       <c r="C113" t="n">
-        <v>218.1999969482422</v>
+        <v>221.5</v>
       </c>
       <c r="D113" t="n">
-        <v>211.7700042724609</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="E113" t="n">
-        <v>216.2599945068359</v>
+        <v>217.8099975585938</v>
       </c>
       <c r="F113" t="n">
-        <v>28545200</v>
+        <v>30694600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="B114" t="n">
-        <v>215.9799957275391</v>
+        <v>210.7799987792969</v>
       </c>
       <c r="C114" t="n">
-        <v>219.1199951171875</v>
+        <v>222.4900054931641</v>
       </c>
       <c r="D114" t="n">
-        <v>214.1399993896484</v>
+        <v>209.0599975585938</v>
       </c>
       <c r="E114" t="n">
-        <v>216.8800048828125</v>
+        <v>218.3699951171875</v>
       </c>
       <c r="F114" t="n">
-        <v>24478200</v>
+        <v>37073900</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45996</v>
+        <v>46006</v>
       </c>
       <c r="B115" t="n">
-        <v>217.9700012207031</v>
+        <v>207.5800018310547</v>
       </c>
       <c r="C115" t="n">
-        <v>223.6399993896484</v>
+        <v>215.3600006103516</v>
       </c>
       <c r="D115" t="n">
-        <v>216.2400054931641</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="E115" t="n">
-        <v>217.1699981689453</v>
+        <v>212.2799987792969</v>
       </c>
       <c r="F115" t="n">
-        <v>33292400</v>
+        <v>27222200</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45999</v>
+        <v>46007</v>
       </c>
       <c r="B116" t="n">
-        <v>221.1100006103516</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="C116" t="n">
-        <v>223.7100067138672</v>
+        <v>210.2200012207031</v>
       </c>
       <c r="D116" t="n">
-        <v>218.3600006103516</v>
+        <v>205.1100006103516</v>
       </c>
       <c r="E116" t="n">
-        <v>219.0899963378906</v>
+        <v>206.9199981689453</v>
       </c>
       <c r="F116" t="n">
-        <v>30943200</v>
+        <v>23467600</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="B117" t="n">
-        <v>221.6199951171875</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="C117" t="n">
-        <v>224.8399963378906</v>
+        <v>211.5</v>
       </c>
       <c r="D117" t="n">
-        <v>217.9100036621094</v>
+        <v>197.5299987792969</v>
       </c>
       <c r="E117" t="n">
-        <v>221.0399932861328</v>
+        <v>210.0399932861328</v>
       </c>
       <c r="F117" t="n">
-        <v>25166100</v>
+        <v>31595400</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="B118" t="n">
-        <v>221.4199981689453</v>
+        <v>201.0599975585938</v>
       </c>
       <c r="C118" t="n">
-        <v>222.6100006103516</v>
+        <v>206.3600006103516</v>
       </c>
       <c r="D118" t="n">
-        <v>218.6699981689453</v>
+        <v>200.5</v>
       </c>
       <c r="E118" t="n">
-        <v>222</v>
+        <v>203.8200073242188</v>
       </c>
       <c r="F118" t="n">
-        <v>23279400</v>
+        <v>29720100</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="B119" t="n">
-        <v>221.4299926757812</v>
+        <v>213.4299926757812</v>
       </c>
       <c r="C119" t="n">
-        <v>221.5</v>
+        <v>215.1799926757812</v>
       </c>
       <c r="D119" t="n">
-        <v>210.1900024414062</v>
+        <v>204.1999969482422</v>
       </c>
       <c r="E119" t="n">
-        <v>217.8099975585938</v>
+        <v>204.6000061035156</v>
       </c>
       <c r="F119" t="n">
-        <v>30694600</v>
+        <v>58445500</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="B120" t="n">
-        <v>210.7799987792969</v>
+        <v>214.9499969482422</v>
       </c>
       <c r="C120" t="n">
-        <v>222.4900054931641</v>
+        <v>220.1699981689453</v>
       </c>
       <c r="D120" t="n">
-        <v>209.0599975585938</v>
+        <v>213.3099975585938</v>
       </c>
       <c r="E120" t="n">
-        <v>218.3699951171875</v>
+        <v>220</v>
       </c>
       <c r="F120" t="n">
-        <v>37073900</v>
+        <v>24950700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="B121" t="n">
-        <v>207.5800018310547</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C121" t="n">
-        <v>215.3600006103516</v>
+        <v>217.0299987792969</v>
       </c>
       <c r="D121" t="n">
-        <v>206.5800018310547</v>
+        <v>212.2799987792969</v>
       </c>
       <c r="E121" t="n">
-        <v>212.2799987792969</v>
+        <v>212.8600006103516</v>
       </c>
       <c r="F121" t="n">
-        <v>27222200</v>
+        <v>20272300</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="B122" t="n">
-        <v>209.1699981689453</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="C122" t="n">
-        <v>210.2200012207031</v>
+        <v>216.5399932861328</v>
       </c>
       <c r="D122" t="n">
-        <v>205.1100006103516</v>
+        <v>213.9700012207031</v>
       </c>
       <c r="E122" t="n">
-        <v>206.9199981689453</v>
+        <v>214.9799957275391</v>
       </c>
       <c r="F122" t="n">
-        <v>23467600</v>
+        <v>7956800</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46008</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>198.1100006103516</v>
+        <v>214.9900054931641</v>
       </c>
       <c r="C123" t="n">
-        <v>211.5</v>
+        <v>216.8300018310547</v>
       </c>
       <c r="D123" t="n">
-        <v>197.5299987792969</v>
+        <v>213.0299987792969</v>
       </c>
       <c r="E123" t="n">
-        <v>210.0399932861328</v>
+        <v>215.4299926757812</v>
       </c>
       <c r="F123" t="n">
-        <v>31595400</v>
+        <v>15792600</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>201.0599975585938</v>
+        <v>215.6100006103516</v>
       </c>
       <c r="C124" t="n">
-        <v>206.3600006103516</v>
+        <v>216.0500030517578</v>
       </c>
       <c r="D124" t="n">
-        <v>200.5</v>
+        <v>209.2400054931641</v>
       </c>
       <c r="E124" t="n">
-        <v>203.8200073242188</v>
+        <v>211.5800018310547</v>
       </c>
       <c r="F124" t="n">
-        <v>29720100</v>
+        <v>20326900</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>213.4299926757812</v>
+        <v>215.3399963378906</v>
       </c>
       <c r="C125" t="n">
-        <v>215.1799926757812</v>
+        <v>216.8200073242188</v>
       </c>
       <c r="D125" t="n">
-        <v>204.1999969482422</v>
+        <v>214.3300018310547</v>
       </c>
       <c r="E125" t="n">
-        <v>204.6000061035156</v>
+        <v>215.8699951171875</v>
       </c>
       <c r="F125" t="n">
-        <v>58445500</v>
+        <v>16409600</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="n">
-        <v>214.9499969482422</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="C126" t="n">
-        <v>220.1699981689453</v>
+        <v>217.6399993896484</v>
       </c>
       <c r="D126" t="n">
-        <v>213.3099975585938</v>
+        <v>213.8000030517578</v>
       </c>
       <c r="E126" t="n">
-        <v>220</v>
+        <v>215.8200073242188</v>
       </c>
       <c r="F126" t="n">
-        <v>24950700</v>
+        <v>17591600</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46014</v>
+        <v>46024</v>
       </c>
       <c r="B127" t="n">
-        <v>214.8999938964844</v>
+        <v>223.4700012207031</v>
       </c>
       <c r="C127" t="n">
-        <v>217.0299987792969</v>
+        <v>227.1499938964844</v>
       </c>
       <c r="D127" t="n">
-        <v>212.2799987792969</v>
+        <v>218.8999938964844</v>
       </c>
       <c r="E127" t="n">
-        <v>212.8600006103516</v>
+        <v>218.8999938964844</v>
       </c>
       <c r="F127" t="n">
-        <v>20272300</v>
+        <v>36446200</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="B128" t="n">
-        <v>215.0399932861328</v>
+        <v>221.0800018310547</v>
       </c>
       <c r="C128" t="n">
-        <v>216.5399932861328</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="D128" t="n">
-        <v>213.9700012207031</v>
+        <v>220.4799957275391</v>
       </c>
       <c r="E128" t="n">
-        <v>214.9799957275391</v>
+        <v>230.25</v>
       </c>
       <c r="F128" t="n">
-        <v>7956800</v>
+        <v>31941100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017</v>
+        <v>46028</v>
       </c>
       <c r="B129" t="n">
-        <v>214.9900054931641</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="C129" t="n">
-        <v>216.8300018310547</v>
+        <v>222.9199981689453</v>
       </c>
       <c r="D129" t="n">
-        <v>213.0299987792969</v>
+        <v>211.25</v>
       </c>
       <c r="E129" t="n">
-        <v>215.4299926757812</v>
+        <v>222.7100067138672</v>
       </c>
       <c r="F129" t="n">
-        <v>15792600</v>
+        <v>40033200</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="B130" t="n">
-        <v>215.6100006103516</v>
+        <v>210.0200042724609</v>
       </c>
       <c r="C130" t="n">
-        <v>216.0500030517578</v>
+        <v>212.1300048828125</v>
       </c>
       <c r="D130" t="n">
-        <v>209.2400054931641</v>
+        <v>207.1699981689453</v>
       </c>
       <c r="E130" t="n">
-        <v>211.5800018310547</v>
+        <v>212.1300048828125</v>
       </c>
       <c r="F130" t="n">
-        <v>20326900</v>
+        <v>29715500</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46021</v>
+        <v>46030</v>
       </c>
       <c r="B131" t="n">
-        <v>215.3399963378906</v>
+        <v>204.6799926757812</v>
       </c>
       <c r="C131" t="n">
-        <v>216.8200073242188</v>
+        <v>210.9400024414062</v>
       </c>
       <c r="D131" t="n">
-        <v>214.3300018310547</v>
+        <v>203.3300018310547</v>
       </c>
       <c r="E131" t="n">
-        <v>215.8699951171875</v>
+        <v>210.8999938964844</v>
       </c>
       <c r="F131" t="n">
-        <v>16409600</v>
+        <v>27505000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="B132" t="n">
-        <v>214.1600036621094</v>
+        <v>203.1699981689453</v>
       </c>
       <c r="C132" t="n">
-        <v>217.6399993896484</v>
+        <v>207.3000030517578</v>
       </c>
       <c r="D132" t="n">
-        <v>213.8000030517578</v>
+        <v>203.0700073242188</v>
       </c>
       <c r="E132" t="n">
-        <v>215.8200073242188</v>
+        <v>205.7200012207031</v>
       </c>
       <c r="F132" t="n">
-        <v>17591600</v>
+        <v>24217300</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="B133" t="n">
-        <v>223.4700012207031</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="C133" t="n">
-        <v>227.1499938964844</v>
+        <v>209.8800048828125</v>
       </c>
       <c r="D133" t="n">
-        <v>218.8999938964844</v>
+        <v>199.8000030517578</v>
       </c>
       <c r="E133" t="n">
-        <v>218.8999938964844</v>
+        <v>201.1799926757812</v>
       </c>
       <c r="F133" t="n">
-        <v>36446200</v>
+        <v>27287300</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46027</v>
+        <v>46035</v>
       </c>
       <c r="B134" t="n">
-        <v>221.0800018310547</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="C134" t="n">
-        <v>234.0200042724609</v>
+        <v>223.1100006103516</v>
       </c>
       <c r="D134" t="n">
-        <v>220.4799957275391</v>
+        <v>214.9799957275391</v>
       </c>
       <c r="E134" t="n">
-        <v>230.25</v>
+        <v>215.1000061035156</v>
       </c>
       <c r="F134" t="n">
-        <v>31941100</v>
+        <v>56894900</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="B135" t="n">
-        <v>214.3500061035156</v>
+        <v>223.6000061035156</v>
       </c>
       <c r="C135" t="n">
-        <v>222.9199981689453</v>
+        <v>224.0899963378906</v>
       </c>
       <c r="D135" t="n">
-        <v>211.25</v>
+        <v>215.1100006103516</v>
       </c>
       <c r="E135" t="n">
-        <v>222.7100067138672</v>
+        <v>217.5399932861328</v>
       </c>
       <c r="F135" t="n">
-        <v>40033200</v>
+        <v>40466500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="B136" t="n">
-        <v>210.0200042724609</v>
+        <v>227.9199981689453</v>
       </c>
       <c r="C136" t="n">
-        <v>212.1300048828125</v>
+        <v>238.3500061035156</v>
       </c>
       <c r="D136" t="n">
-        <v>207.1699981689453</v>
+        <v>227.2200012207031</v>
       </c>
       <c r="E136" t="n">
-        <v>212.1300048828125</v>
+        <v>227.8999938964844</v>
       </c>
       <c r="F136" t="n">
-        <v>29715500</v>
+        <v>55270200</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="B137" t="n">
-        <v>204.6799926757812</v>
+        <v>231.8300018310547</v>
       </c>
       <c r="C137" t="n">
-        <v>210.9400024414062</v>
+        <v>234.4900054931641</v>
       </c>
       <c r="D137" t="n">
-        <v>203.3300018310547</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="E137" t="n">
-        <v>210.8999938964844</v>
+        <v>234.3000030517578</v>
       </c>
       <c r="F137" t="n">
-        <v>27505000</v>
+        <v>42545600</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>203.1699981689453</v>
+        <v>231.9199981689453</v>
       </c>
       <c r="C138" t="n">
-        <v>207.3000030517578</v>
+        <v>239.5</v>
       </c>
       <c r="D138" t="n">
-        <v>203.0700073242188</v>
+        <v>225.4100036621094</v>
       </c>
       <c r="E138" t="n">
-        <v>205.7200012207031</v>
+        <v>226.0800018310547</v>
       </c>
       <c r="F138" t="n">
-        <v>24217300</v>
+        <v>44327700</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46034</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>207.6900024414062</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="C139" t="n">
-        <v>209.8800048828125</v>
+        <v>252.8999938964844</v>
       </c>
       <c r="D139" t="n">
-        <v>199.8000030517578</v>
+        <v>235.7799987792969</v>
       </c>
       <c r="E139" t="n">
-        <v>201.1799926757812</v>
+        <v>235.9900054931641</v>
       </c>
       <c r="F139" t="n">
-        <v>27287300</v>
+        <v>62385600</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46035</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>220.9700012207031</v>
+        <v>253.7299957275391</v>
       </c>
       <c r="C140" t="n">
-        <v>223.1100006103516</v>
+        <v>256.0799865722656</v>
       </c>
       <c r="D140" t="n">
-        <v>214.9799957275391</v>
+        <v>246.6300048828125</v>
       </c>
       <c r="E140" t="n">
-        <v>215.1000061035156</v>
+        <v>251.75</v>
       </c>
       <c r="F140" t="n">
-        <v>56894900</v>
+        <v>37945000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>223.6000061035156</v>
+        <v>259.6799926757812</v>
       </c>
       <c r="C141" t="n">
-        <v>224.0899963378906</v>
+        <v>266.9599914550781</v>
       </c>
       <c r="D141" t="n">
-        <v>215.1100006103516</v>
+        <v>256.25</v>
       </c>
       <c r="E141" t="n">
-        <v>217.5399932861328</v>
+        <v>261.1799926757812</v>
       </c>
       <c r="F141" t="n">
-        <v>40466500</v>
+        <v>47525900</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>227.9199981689453</v>
+        <v>251.3099975585938</v>
       </c>
       <c r="C142" t="n">
-        <v>238.3500061035156</v>
+        <v>258.2900085449219</v>
       </c>
       <c r="D142" t="n">
-        <v>227.2200012207031</v>
+        <v>250.3000030517578</v>
       </c>
       <c r="E142" t="n">
-        <v>227.8999938964844</v>
+        <v>256.75</v>
       </c>
       <c r="F142" t="n">
-        <v>55270200</v>
+        <v>30672500</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>231.8300018310547</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="C143" t="n">
-        <v>234.4900054931641</v>
+        <v>255.5500030517578</v>
       </c>
       <c r="D143" t="n">
-        <v>228.8600006103516</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="E143" t="n">
-        <v>234.3000030517578</v>
+        <v>252.1600036621094</v>
       </c>
       <c r="F143" t="n">
-        <v>42545600</v>
+        <v>25691600</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>231.9199981689453</v>
+        <v>252.7400054931641</v>
       </c>
       <c r="C144" t="n">
-        <v>239.5</v>
+        <v>257.3999938964844</v>
       </c>
       <c r="D144" t="n">
-        <v>225.4100036621094</v>
+        <v>250.2100067138672</v>
       </c>
       <c r="E144" t="n">
-        <v>226.0800018310547</v>
+        <v>254.1300048828125</v>
       </c>
       <c r="F144" t="n">
-        <v>44327700</v>
+        <v>27061200</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46043</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>249.8000030517578</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="C145" t="n">
-        <v>252.8999938964844</v>
+        <v>260.5299987792969</v>
       </c>
       <c r="D145" t="n">
-        <v>235.7799987792969</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="E145" t="n">
-        <v>235.9900054931641</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="F145" t="n">
-        <v>62385600</v>
+        <v>31685200</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>253.7299957275391</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="C146" t="n">
-        <v>256.0799865722656</v>
+        <v>245.2400054931641</v>
       </c>
       <c r="D146" t="n">
-        <v>246.6300048828125</v>
+        <v>234.5500030517578</v>
       </c>
       <c r="E146" t="n">
-        <v>251.75</v>
+        <v>236.9299926757812</v>
       </c>
       <c r="F146" t="n">
-        <v>37945000</v>
+        <v>40035700</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>259.6799926757812</v>
+        <v>246.2700042724609</v>
       </c>
       <c r="C147" t="n">
-        <v>266.9599914550781</v>
+        <v>249.9700012207031</v>
       </c>
       <c r="D147" t="n">
-        <v>256.25</v>
+        <v>235</v>
       </c>
       <c r="E147" t="n">
-        <v>261.1799926757812</v>
+        <v>235.7700042724609</v>
       </c>
       <c r="F147" t="n">
-        <v>47525900</v>
+        <v>36308100</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>251.3099975585938</v>
+        <v>242.1100006103516</v>
       </c>
       <c r="C148" t="n">
-        <v>258.2900085449219</v>
+        <v>252.6499938964844</v>
       </c>
       <c r="D148" t="n">
-        <v>250.3000030517578</v>
+        <v>237.0399932861328</v>
       </c>
       <c r="E148" t="n">
-        <v>256.75</v>
+        <v>251.5500030517578</v>
       </c>
       <c r="F148" t="n">
-        <v>30672500</v>
+        <v>53097100</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>252.0299987792969</v>
+        <v>200.1900024414062</v>
       </c>
       <c r="C149" t="n">
-        <v>255.5500030517578</v>
+        <v>218.5800018310547</v>
       </c>
       <c r="D149" t="n">
-        <v>247.9600067138672</v>
+        <v>199.1499938964844</v>
       </c>
       <c r="E149" t="n">
-        <v>252.1600036621094</v>
+        <v>215</v>
       </c>
       <c r="F149" t="n">
-        <v>25691600</v>
+        <v>107173300</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>252.7400054931641</v>
+        <v>192.5</v>
       </c>
       <c r="C150" t="n">
-        <v>257.3999938964844</v>
+        <v>204.0399932861328</v>
       </c>
       <c r="D150" t="n">
-        <v>250.2100067138672</v>
+        <v>190.7200012207031</v>
       </c>
       <c r="E150" t="n">
-        <v>254.1300048828125</v>
+        <v>201.8600006103516</v>
       </c>
       <c r="F150" t="n">
-        <v>27061200</v>
+        <v>62196400</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>252.1799926757812</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="C151" t="n">
-        <v>260.5299987792969</v>
+        <v>209.2700042724609</v>
       </c>
       <c r="D151" t="n">
-        <v>240.9100036621094</v>
+        <v>196.4299926757812</v>
       </c>
       <c r="E151" t="n">
-        <v>254.6600036621094</v>
+        <v>197.1300048828125</v>
       </c>
       <c r="F151" t="n">
-        <v>31685200</v>
+        <v>54504500</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>236.7299957275391</v>
+        <v>216</v>
       </c>
       <c r="C152" t="n">
-        <v>245.2400054931641</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="D152" t="n">
-        <v>234.5500030517578</v>
+        <v>204.1499938964844</v>
       </c>
       <c r="E152" t="n">
-        <v>236.9299926757812</v>
+        <v>206.8999938964844</v>
       </c>
       <c r="F152" t="n">
-        <v>40035700</v>
+        <v>38810800</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>246.2700042724609</v>
+        <v>213.5700073242188</v>
       </c>
       <c r="C153" t="n">
-        <v>249.9700012207031</v>
+        <v>219.3899993896484</v>
       </c>
       <c r="D153" t="n">
-        <v>235</v>
+        <v>213.1300048828125</v>
       </c>
       <c r="E153" t="n">
-        <v>235.7700042724609</v>
+        <v>215.1399993896484</v>
       </c>
       <c r="F153" t="n">
-        <v>36308100</v>
+        <v>25326700</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>242.1100006103516</v>
+        <v>213.5800018310547</v>
       </c>
       <c r="C154" t="n">
-        <v>252.6499938964844</v>
+        <v>219.6499938964844</v>
       </c>
       <c r="D154" t="n">
-        <v>237.0399932861328</v>
+        <v>209.2100067138672</v>
       </c>
       <c r="E154" t="n">
-        <v>251.5500030517578</v>
+        <v>217.8800048828125</v>
       </c>
       <c r="F154" t="n">
-        <v>53097100</v>
+        <v>33384700</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>200.1900024414062</v>
+        <v>205.9400024414062</v>
       </c>
       <c r="C155" t="n">
-        <v>218.5800018310547</v>
+        <v>218.4600067138672</v>
       </c>
       <c r="D155" t="n">
-        <v>199.1499938964844</v>
+        <v>205.1399993896484</v>
       </c>
       <c r="E155" t="n">
-        <v>215</v>
+        <v>215.8300018310547</v>
       </c>
       <c r="F155" t="n">
-        <v>107173300</v>
+        <v>32181000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>192.5</v>
+        <v>207.3200073242188</v>
       </c>
       <c r="C156" t="n">
-        <v>204.0399932861328</v>
+        <v>210.0500030517578</v>
       </c>
       <c r="D156" t="n">
-        <v>190.7200012207031</v>
+        <v>203.8800048828125</v>
       </c>
       <c r="E156" t="n">
-        <v>201.8600006103516</v>
+        <v>204.0200042724609</v>
       </c>
       <c r="F156" t="n">
-        <v>62196400</v>
+        <v>26123900</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="B157" t="n">
-        <v>208.4400024414062</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C157" t="n">
-        <v>209.2700042724609</v>
+        <v>205.3000030517578</v>
       </c>
       <c r="D157" t="n">
-        <v>196.4299926757812</v>
+        <v>194.8300018310547</v>
       </c>
       <c r="E157" t="n">
-        <v>197.1300048828125</v>
+        <v>202.1499938964844</v>
       </c>
       <c r="F157" t="n">
-        <v>54504500</v>
+        <v>33712100</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="n">
-        <v>216</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="C158" t="n">
-        <v>217.6000061035156</v>
+        <v>203.1999969482422</v>
       </c>
       <c r="D158" t="n">
-        <v>204.1499938964844</v>
+        <v>195</v>
       </c>
       <c r="E158" t="n">
-        <v>206.8999938964844</v>
+        <v>198.4100036621094</v>
       </c>
       <c r="F158" t="n">
-        <v>38810800</v>
+        <v>35664100</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="B159" t="n">
-        <v>213.5700073242188</v>
+        <v>203.3699951171875</v>
       </c>
       <c r="C159" t="n">
-        <v>219.3899993896484</v>
+        <v>204.1000061035156</v>
       </c>
       <c r="D159" t="n">
-        <v>213.1300048828125</v>
+        <v>198.2899932861328</v>
       </c>
       <c r="E159" t="n">
-        <v>215.1399993896484</v>
+        <v>200.1100006103516</v>
       </c>
       <c r="F159" t="n">
-        <v>25326700</v>
+        <v>25842300</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46064</v>
+        <v>46073</v>
       </c>
       <c r="B160" t="n">
-        <v>213.5800018310547</v>
+        <v>200.1499938964844</v>
       </c>
       <c r="C160" t="n">
-        <v>219.6499938964844</v>
+        <v>204.8699951171875</v>
       </c>
       <c r="D160" t="n">
-        <v>209.2100067138672</v>
+        <v>198.5599975585938</v>
       </c>
       <c r="E160" t="n">
-        <v>217.8800048828125</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="F160" t="n">
-        <v>33384700</v>
+        <v>36317300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="B161" t="n">
-        <v>205.9400024414062</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="C161" t="n">
-        <v>218.4600067138672</v>
+        <v>199.3800048828125</v>
       </c>
       <c r="D161" t="n">
-        <v>205.1399993896484</v>
+        <v>194.1499938964844</v>
       </c>
       <c r="E161" t="n">
-        <v>215.8300018310547</v>
+        <v>198.0899963378906</v>
       </c>
       <c r="F161" t="n">
-        <v>32181000</v>
+        <v>28187900</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B162" t="n">
-        <v>207.3200073242188</v>
+        <v>213.8399963378906</v>
       </c>
       <c r="C162" t="n">
-        <v>210.0500030517578</v>
+        <v>216.7100067138672</v>
       </c>
       <c r="D162" t="n">
-        <v>203.8800048828125</v>
+        <v>206.5</v>
       </c>
       <c r="E162" t="n">
-        <v>204.0200042724609</v>
+        <v>211.6300048828125</v>
       </c>
       <c r="F162" t="n">
-        <v>26123900</v>
+        <v>81367000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="B163" t="n">
-        <v>203.0800018310547</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="C163" t="n">
-        <v>205.3000030517578</v>
+        <v>216.6999969482422</v>
       </c>
       <c r="D163" t="n">
-        <v>194.8300018310547</v>
+        <v>210.3300018310547</v>
       </c>
       <c r="E163" t="n">
-        <v>202.1499938964844</v>
+        <v>214.8200073242188</v>
       </c>
       <c r="F163" t="n">
-        <v>33712100</v>
+        <v>44588100</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="B164" t="n">
-        <v>200.1199951171875</v>
+        <v>203.6799926757812</v>
       </c>
       <c r="C164" t="n">
-        <v>203.1999969482422</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="D164" t="n">
-        <v>195</v>
+        <v>201.4600067138672</v>
       </c>
       <c r="E164" t="n">
-        <v>198.4100036621094</v>
+        <v>208.8000030517578</v>
       </c>
       <c r="F164" t="n">
-        <v>35664100</v>
+        <v>35020500</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="B165" t="n">
-        <v>203.3699951171875</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="C165" t="n">
-        <v>204.1000061035156</v>
+        <v>201.8899993896484</v>
       </c>
       <c r="D165" t="n">
-        <v>198.2899932861328</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="E165" t="n">
         <v>200.1100006103516</v>
       </c>
       <c r="F165" t="n">
-        <v>25842300</v>
+        <v>31312400</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="B166" t="n">
-        <v>200.1499938964844</v>
+        <v>198.6199951171875</v>
       </c>
       <c r="C166" t="n">
-        <v>204.8699951171875</v>
+        <v>198.7400054931641</v>
       </c>
       <c r="D166" t="n">
-        <v>198.5599975585938</v>
+        <v>190</v>
       </c>
       <c r="E166" t="n">
-        <v>200.1199951171875</v>
+        <v>193.8500061035156</v>
       </c>
       <c r="F166" t="n">
-        <v>36317300</v>
+        <v>34120200</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B167" t="n">
-        <v>196.6000061035156</v>
+        <v>190.9499969482422</v>
       </c>
       <c r="C167" t="n">
-        <v>199.3800048828125</v>
+        <v>193.6399993896484</v>
       </c>
       <c r="D167" t="n">
-        <v>194.1499938964844</v>
+        <v>188.2200012207031</v>
       </c>
       <c r="E167" t="n">
-        <v>198.0899963378906</v>
+        <v>191.4600067138672</v>
       </c>
       <c r="F167" t="n">
-        <v>28187900</v>
+        <v>37785700</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B168" t="n">
-        <v>213.8399963378906</v>
+        <v>202.0700073242188</v>
       </c>
       <c r="C168" t="n">
-        <v>216.7100067138672</v>
+        <v>202.4400024414062</v>
       </c>
       <c r="D168" t="n">
-        <v>206.5</v>
+        <v>189.8600006103516</v>
       </c>
       <c r="E168" t="n">
-        <v>211.6300048828125</v>
+        <v>192.1199951171875</v>
       </c>
       <c r="F168" t="n">
-        <v>81367000</v>
+        <v>40912600</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B169" t="n">
-        <v>210.8600006103516</v>
+        <v>199.4499969482422</v>
       </c>
       <c r="C169" t="n">
-        <v>216.6999969482422</v>
+        <v>203.7899932861328</v>
       </c>
       <c r="D169" t="n">
-        <v>210.3300018310547</v>
+        <v>194.8800048828125</v>
       </c>
       <c r="E169" t="n">
-        <v>214.8200073242188</v>
+        <v>197.7700042724609</v>
       </c>
       <c r="F169" t="n">
-        <v>44588100</v>
+        <v>36000700</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B170" t="n">
-        <v>203.6799926757812</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="C170" t="n">
-        <v>209.7899932861328</v>
+        <v>200.2400054931641</v>
       </c>
       <c r="D170" t="n">
-        <v>201.4600067138672</v>
+        <v>191.25</v>
       </c>
       <c r="E170" t="n">
-        <v>208.8000030517578</v>
+        <v>195.2700042724609</v>
       </c>
       <c r="F170" t="n">
-        <v>35020500</v>
+        <v>33913800</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>200.2100067138672</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C171" t="n">
-        <v>201.8899993896484</v>
+        <v>202.9700012207031</v>
       </c>
       <c r="D171" t="n">
-        <v>197.7400054931641</v>
+        <v>189.0200042724609</v>
       </c>
       <c r="E171" t="n">
-        <v>200.1100006103516</v>
+        <v>189.3600006103516</v>
       </c>
       <c r="F171" t="n">
-        <v>31312400</v>
+        <v>38877200</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>198.6199951171875</v>
+        <v>203.2299957275391</v>
       </c>
       <c r="C172" t="n">
-        <v>198.7400054931641</v>
+        <v>206.5899963378906</v>
       </c>
       <c r="D172" t="n">
-        <v>190</v>
+        <v>202.1999969482422</v>
       </c>
       <c r="E172" t="n">
-        <v>193.8500061035156</v>
+        <v>202.5099945068359</v>
       </c>
       <c r="F172" t="n">
-        <v>34120200</v>
+        <v>29139200</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>190.9499969482422</v>
+        <v>204.8300018310547</v>
       </c>
       <c r="C173" t="n">
-        <v>193.6399993896484</v>
+        <v>209.2100067138672</v>
       </c>
       <c r="D173" t="n">
-        <v>188.2200012207031</v>
+        <v>203.6300048828125</v>
       </c>
       <c r="E173" t="n">
-        <v>191.4600067138672</v>
+        <v>205.1100006103516</v>
       </c>
       <c r="F173" t="n">
-        <v>37785700</v>
+        <v>23076400</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>202.0700073242188</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="C174" t="n">
-        <v>202.4400024414062</v>
+        <v>203.6199951171875</v>
       </c>
       <c r="D174" t="n">
-        <v>189.8600006103516</v>
+        <v>196.6699981689453</v>
       </c>
       <c r="E174" t="n">
-        <v>192.1199951171875</v>
+        <v>202.8300018310547</v>
       </c>
       <c r="F174" t="n">
-        <v>40912600</v>
+        <v>28886900</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>199.4499969482422</v>
+        <v>193.3899993896484</v>
       </c>
       <c r="C175" t="n">
-        <v>203.7899932861328</v>
+        <v>199.6799926757812</v>
       </c>
       <c r="D175" t="n">
-        <v>194.8800048828125</v>
+        <v>192.2700042724609</v>
       </c>
       <c r="E175" t="n">
-        <v>197.7700042724609</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="F175" t="n">
-        <v>36000700</v>
+        <v>27561900</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="B176" t="n">
-        <v>192.4299926757812</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="C176" t="n">
-        <v>200.2400054931641</v>
+        <v>200.1699981689453</v>
       </c>
       <c r="D176" t="n">
-        <v>191.25</v>
+        <v>194.8000030517578</v>
       </c>
       <c r="E176" t="n">
-        <v>195.2700042724609</v>
+        <v>194.9799957275391</v>
       </c>
       <c r="F176" t="n">
-        <v>33913800</v>
+        <v>30285200</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="B177" t="n">
-        <v>202.6799926757812</v>
+        <v>196.3099975585938</v>
       </c>
       <c r="C177" t="n">
-        <v>202.9700012207031</v>
+        <v>199.2100067138672</v>
       </c>
       <c r="D177" t="n">
-        <v>189.0200042724609</v>
+        <v>195.2599945068359</v>
       </c>
       <c r="E177" t="n">
-        <v>189.3600006103516</v>
+        <v>196.6799926757812</v>
       </c>
       <c r="F177" t="n">
-        <v>38877200</v>
+        <v>22779700</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="B178" t="n">
-        <v>203.2299957275391</v>
+        <v>199.4600067138672</v>
       </c>
       <c r="C178" t="n">
-        <v>206.5899963378906</v>
+        <v>202.8600006103516</v>
       </c>
       <c r="D178" t="n">
-        <v>202.1999969482422</v>
+        <v>195.75</v>
       </c>
       <c r="E178" t="n">
-        <v>202.5099945068359</v>
+        <v>196</v>
       </c>
       <c r="F178" t="n">
-        <v>29139200</v>
+        <v>28569100</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="B179" t="n">
-        <v>204.8300018310547</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C179" t="n">
-        <v>209.2100067138672</v>
+        <v>205.8800048828125</v>
       </c>
       <c r="D179" t="n">
-        <v>203.6300048828125</v>
+        <v>192.8300018310547</v>
       </c>
       <c r="E179" t="n">
-        <v>205.1100006103516</v>
+        <v>195.0299987792969</v>
       </c>
       <c r="F179" t="n">
-        <v>23076400</v>
+        <v>32245300</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="B180" t="n">
-        <v>197.7400054931641</v>
+        <v>201.3300018310547</v>
       </c>
       <c r="C180" t="n">
-        <v>203.6199951171875</v>
+        <v>206.3000030517578</v>
       </c>
       <c r="D180" t="n">
-        <v>196.6699981689453</v>
+        <v>198.2599945068359</v>
       </c>
       <c r="E180" t="n">
-        <v>202.8300018310547</v>
+        <v>204.8899993896484</v>
       </c>
       <c r="F180" t="n">
-        <v>28886900</v>
+        <v>37265100</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="B181" t="n">
-        <v>193.3899993896484</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C181" t="n">
-        <v>199.6799926757812</v>
+        <v>209.1100006103516</v>
       </c>
       <c r="D181" t="n">
-        <v>192.2700042724609</v>
+        <v>201.7100067138672</v>
       </c>
       <c r="E181" t="n">
-        <v>198.1100006103516</v>
+        <v>206.3999938964844</v>
       </c>
       <c r="F181" t="n">
-        <v>27561900</v>
+        <v>31857800</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="B182" t="n">
-        <v>196.5800018310547</v>
+        <v>205.3699951171875</v>
       </c>
       <c r="C182" t="n">
-        <v>200.1699981689453</v>
+        <v>206.4299926757812</v>
       </c>
       <c r="D182" t="n">
-        <v>194.8000030517578</v>
+        <v>200.1300048828125</v>
       </c>
       <c r="E182" t="n">
-        <v>194.9799957275391</v>
+        <v>201.3899993896484</v>
       </c>
       <c r="F182" t="n">
-        <v>30285200</v>
+        <v>27258800</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="B183" t="n">
-        <v>196.3099975585938</v>
+        <v>220.2700042724609</v>
       </c>
       <c r="C183" t="n">
-        <v>199.2100067138672</v>
+        <v>221.3300018310547</v>
       </c>
       <c r="D183" t="n">
-        <v>195.2599945068359</v>
+        <v>211.5099945068359</v>
       </c>
       <c r="E183" t="n">
-        <v>196.6799926757812</v>
+        <v>211.5099945068359</v>
       </c>
       <c r="F183" t="n">
-        <v>22779700</v>
+        <v>48518300</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="B184" t="n">
-        <v>199.4600067138672</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="C184" t="n">
-        <v>202.8600006103516</v>
+        <v>221</v>
       </c>
       <c r="D184" t="n">
-        <v>195.75</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="E184" t="n">
-        <v>196</v>
+        <v>217.9799957275391</v>
       </c>
       <c r="F184" t="n">
-        <v>28569100</v>
+        <v>49213000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="B185" t="n">
-        <v>205.2700042724609</v>
+        <v>201.9900054931641</v>
       </c>
       <c r="C185" t="n">
-        <v>205.8800048828125</v>
+        <v>203.2700042724609</v>
       </c>
       <c r="D185" t="n">
-        <v>192.8300018310547</v>
+        <v>197.6900024414062</v>
       </c>
       <c r="E185" t="n">
-        <v>195.0299987792969</v>
+        <v>201.7700042724609</v>
       </c>
       <c r="F185" t="n">
-        <v>32245300</v>
+        <v>29206600</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="B186" t="n">
-        <v>201.3300018310547</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="C186" t="n">
-        <v>206.3000030517578</v>
+        <v>208.4299926757812</v>
       </c>
       <c r="D186" t="n">
-        <v>198.2599945068359</v>
+        <v>192.8699951171875</v>
       </c>
       <c r="E186" t="n">
-        <v>204.8899993896484</v>
+        <v>204.9499969482422</v>
       </c>
       <c r="F186" t="n">
-        <v>37265100</v>
+        <v>41053300</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="B187" t="n">
-        <v>202.6799926757812</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="C187" t="n">
-        <v>209.1100006103516</v>
+        <v>204</v>
       </c>
       <c r="D187" t="n">
-        <v>201.7100067138672</v>
+        <v>196.4100036621094</v>
       </c>
       <c r="E187" t="n">
-        <v>206.3999938964844</v>
+        <v>198.0500030517578</v>
       </c>
       <c r="F187" t="n">
-        <v>31857800</v>
+        <v>42318700</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="B188" t="n">
-        <v>205.3699951171875</v>
+        <v>210.2100067138672</v>
       </c>
       <c r="C188" t="n">
-        <v>206.4299926757812</v>
+        <v>213.8300018310547</v>
       </c>
       <c r="D188" t="n">
-        <v>200.1300048828125</v>
+        <v>205.8399963378906</v>
       </c>
       <c r="E188" t="n">
-        <v>201.3899993896484</v>
+        <v>207.5899963378906</v>
       </c>
       <c r="F188" t="n">
-        <v>27258800</v>
+        <v>40835800</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B189" t="n">
-        <v>220.2700042724609</v>
+        <v>217.5</v>
       </c>
       <c r="C189" t="n">
-        <v>221.3300018310547</v>
+        <v>217.7799987792969</v>
       </c>
       <c r="D189" t="n">
-        <v>211.5099945068359</v>
+        <v>200.6199951171875</v>
       </c>
       <c r="E189" t="n">
-        <v>211.5099945068359</v>
+        <v>204.0500030517578</v>
       </c>
       <c r="F189" t="n">
-        <v>48518300</v>
+        <v>38463500</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B190" t="n">
-        <v>203.7700042724609</v>
+        <v>220.1799926757812</v>
       </c>
       <c r="C190" t="n">
-        <v>221</v>
+        <v>226.3099975585938</v>
       </c>
       <c r="D190" t="n">
-        <v>203.4299926757812</v>
+        <v>217.7299957275391</v>
       </c>
       <c r="E190" t="n">
-        <v>217.9799957275391</v>
+        <v>219.2799987792969</v>
       </c>
       <c r="F190" t="n">
-        <v>49213000</v>
+        <v>30786400</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="B191" t="n">
-        <v>201.9900054931641</v>
+        <v>221.5299987792969</v>
       </c>
       <c r="C191" t="n">
-        <v>203.2700042724609</v>
+        <v>222.1000061035156</v>
       </c>
       <c r="D191" t="n">
-        <v>197.6900024414062</v>
+        <v>215.3800048828125</v>
       </c>
       <c r="E191" t="n">
-        <v>201.7700042724609</v>
+        <v>218.2599945068359</v>
       </c>
       <c r="F191" t="n">
-        <v>29206600</v>
+        <v>26483000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="B192" t="n">
-        <v>196.0399932861328</v>
+        <v>231.8200073242188</v>
       </c>
       <c r="C192" t="n">
-        <v>208.4299926757812</v>
+        <v>234</v>
       </c>
       <c r="D192" t="n">
-        <v>192.8699951171875</v>
+        <v>227.0899963378906</v>
       </c>
       <c r="E192" t="n">
-        <v>204.9499969482422</v>
+        <v>232.1199951171875</v>
       </c>
       <c r="F192" t="n">
-        <v>41053300</v>
+        <v>35496400</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46112</v>
+        <v>46121</v>
       </c>
       <c r="B193" t="n">
-        <v>203.4299926757812</v>
+        <v>236.6399993896484</v>
       </c>
       <c r="C193" t="n">
-        <v>204</v>
+        <v>237.1000061035156</v>
       </c>
       <c r="D193" t="n">
-        <v>196.4100036621094</v>
+        <v>230.9100036621094</v>
       </c>
       <c r="E193" t="n">
-        <v>198.0500030517578</v>
+        <v>233.0099945068359</v>
       </c>
       <c r="F193" t="n">
-        <v>42318700</v>
+        <v>27126200</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="B194" t="n">
-        <v>210.2100067138672</v>
+        <v>245.0399932861328</v>
       </c>
       <c r="C194" t="n">
-        <v>213.8300018310547</v>
+        <v>249.5800018310547</v>
       </c>
       <c r="D194" t="n">
-        <v>205.8399963378906</v>
+        <v>238.9600067138672</v>
       </c>
       <c r="E194" t="n">
-        <v>207.5899963378906</v>
+        <v>239</v>
       </c>
       <c r="F194" t="n">
-        <v>40835800</v>
+        <v>36477200</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="B195" t="n">
-        <v>217.5</v>
+        <v>246.8300018310547</v>
       </c>
       <c r="C195" t="n">
-        <v>217.7799987792969</v>
+        <v>247.3300018310547</v>
       </c>
       <c r="D195" t="n">
-        <v>200.6199951171875</v>
+        <v>242.0299987792969</v>
       </c>
       <c r="E195" t="n">
-        <v>204.0500030517578</v>
+        <v>245.0299987792969</v>
       </c>
       <c r="F195" t="n">
-        <v>38463500</v>
+        <v>22781800</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="B196" t="n">
-        <v>220.1799926757812</v>
+        <v>255.0700073242188</v>
       </c>
       <c r="C196" t="n">
-        <v>226.3099975585938</v>
+        <v>255.4600067138672</v>
       </c>
       <c r="D196" t="n">
-        <v>217.7299957275391</v>
+        <v>245.6999969482422</v>
       </c>
       <c r="E196" t="n">
-        <v>219.2799987792969</v>
+        <v>249.7899932861328</v>
       </c>
       <c r="F196" t="n">
-        <v>30786400</v>
+        <v>25733200</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="B197" t="n">
-        <v>221.5299987792969</v>
+        <v>258.1199951171875</v>
       </c>
       <c r="C197" t="n">
-        <v>222.1000061035156</v>
+        <v>258.1799926757812</v>
       </c>
       <c r="D197" t="n">
-        <v>215.3800048828125</v>
+        <v>251.8500061035156</v>
       </c>
       <c r="E197" t="n">
-        <v>218.2599945068359</v>
+        <v>254.9600067138672</v>
       </c>
       <c r="F197" t="n">
-        <v>26483000</v>
+        <v>24695200</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="B198" t="n">
-        <v>231.8200073242188</v>
+        <v>278.260009765625</v>
       </c>
       <c r="C198" t="n">
-        <v>234</v>
+        <v>279.3399963378906</v>
       </c>
       <c r="D198" t="n">
-        <v>227.0899963378906</v>
+        <v>261.510009765625</v>
       </c>
       <c r="E198" t="n">
-        <v>232.1199951171875</v>
+        <v>264.989990234375</v>
       </c>
       <c r="F198" t="n">
-        <v>35496400</v>
+        <v>64850800</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="B199" t="n">
-        <v>236.6399993896484</v>
+        <v>278.3900146484375</v>
       </c>
       <c r="C199" t="n">
-        <v>237.1000061035156</v>
+        <v>281.0499877929688</v>
       </c>
       <c r="D199" t="n">
-        <v>230.9100036621094</v>
+        <v>274.1400146484375</v>
       </c>
       <c r="E199" t="n">
-        <v>233.0099945068359</v>
+        <v>281</v>
       </c>
       <c r="F199" t="n">
-        <v>27126200</v>
+        <v>35519900</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="n">
-        <v>245.0399932861328</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C200" t="n">
-        <v>249.5800018310547</v>
+        <v>287.6099853515625</v>
       </c>
       <c r="D200" t="n">
-        <v>238.9600067138672</v>
+        <v>272</v>
       </c>
       <c r="E200" t="n">
-        <v>239</v>
+        <v>280.6000061035156</v>
       </c>
       <c r="F200" t="n">
-        <v>36477200</v>
+        <v>34833900</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="B201" t="n">
-        <v>246.8300018310547</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C201" t="n">
-        <v>247.3300018310547</v>
+        <v>286.2000122070312</v>
       </c>
       <c r="D201" t="n">
-        <v>242.0299987792969</v>
+        <v>276.6199951171875</v>
       </c>
       <c r="E201" t="n">
-        <v>245.0299987792969</v>
+        <v>277.3299865722656</v>
       </c>
       <c r="F201" t="n">
-        <v>22781800</v>
+        <v>38950900</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="B202" t="n">
-        <v>255.0700073242188</v>
+        <v>303.4599914550781</v>
       </c>
       <c r="C202" t="n">
-        <v>255.4600067138672</v>
+        <v>304.25</v>
       </c>
       <c r="D202" t="n">
-        <v>245.6999969482422</v>
+        <v>286.1400146484375</v>
       </c>
       <c r="E202" t="n">
-        <v>249.7899932861328</v>
+        <v>291.2200012207031</v>
       </c>
       <c r="F202" t="n">
-        <v>25733200</v>
+        <v>49054200</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B203" t="n">
-        <v>258.1199951171875</v>
+        <v>305.3299865722656</v>
       </c>
       <c r="C203" t="n">
-        <v>258.1799926757812</v>
+        <v>310.2200012207031</v>
       </c>
       <c r="D203" t="n">
-        <v>251.8500061035156</v>
+        <v>299.760009765625</v>
       </c>
       <c r="E203" t="n">
-        <v>254.9600067138672</v>
+        <v>302.010009765625</v>
       </c>
       <c r="F203" t="n">
-        <v>24695200</v>
+        <v>45619700</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="B204" t="n">
-        <v>278.260009765625</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="C204" t="n">
-        <v>279.3399963378906</v>
+        <v>352.989990234375</v>
       </c>
       <c r="D204" t="n">
-        <v>261.510009765625</v>
+        <v>334.5400085449219</v>
       </c>
       <c r="E204" t="n">
-        <v>264.989990234375</v>
+        <v>336.760009765625</v>
       </c>
       <c r="F204" t="n">
-        <v>64850800</v>
+        <v>81616700</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46129</v>
+        <v>46139</v>
       </c>
       <c r="B205" t="n">
-        <v>278.3900146484375</v>
+        <v>334.6300048828125</v>
       </c>
       <c r="C205" t="n">
-        <v>281.0499877929688</v>
+        <v>349.2099914550781</v>
       </c>
       <c r="D205" t="n">
-        <v>274.1400146484375</v>
+        <v>328.8099975585938</v>
       </c>
       <c r="E205" t="n">
-        <v>281</v>
+        <v>346.3200073242188</v>
       </c>
       <c r="F205" t="n">
-        <v>35519900</v>
+        <v>50585300</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="B206" t="n">
-        <v>274.9500122070312</v>
+        <v>323.2099914550781</v>
       </c>
       <c r="C206" t="n">
-        <v>287.6099853515625</v>
+        <v>327.5</v>
       </c>
       <c r="D206" t="n">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="E206" t="n">
-        <v>280.6000061035156</v>
+        <v>311.8599853515625</v>
       </c>
       <c r="F206" t="n">
-        <v>34833900</v>
+        <v>43002500</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="B207" t="n">
-        <v>284.489990234375</v>
+        <v>337.1099853515625</v>
       </c>
       <c r="C207" t="n">
-        <v>286.2000122070312</v>
+        <v>340.1700134277344</v>
       </c>
       <c r="D207" t="n">
-        <v>276.6199951171875</v>
+        <v>318.8599853515625</v>
       </c>
       <c r="E207" t="n">
-        <v>277.3299865722656</v>
+        <v>326.5799865722656</v>
       </c>
       <c r="F207" t="n">
-        <v>38950900</v>
+        <v>44704400</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="B208" t="n">
-        <v>303.4599914550781</v>
+        <v>354.489990234375</v>
       </c>
       <c r="C208" t="n">
-        <v>304.25</v>
+        <v>354.9599914550781</v>
       </c>
       <c r="D208" t="n">
-        <v>286.1400146484375</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="E208" t="n">
-        <v>291.2200012207031</v>
+        <v>341.3599853515625</v>
       </c>
       <c r="F208" t="n">
-        <v>49054200</v>
+        <v>42115300</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B209" t="n">
-        <v>305.3299865722656</v>
+        <v>360.5400085449219</v>
       </c>
       <c r="C209" t="n">
-        <v>310.2200012207031</v>
+        <v>362.7900085449219</v>
       </c>
       <c r="D209" t="n">
-        <v>299.760009765625</v>
+        <v>349.25</v>
       </c>
       <c r="E209" t="n">
-        <v>302.010009765625</v>
+        <v>351.8699951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>45619700</v>
+        <v>34279200</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="B210" t="n">
-        <v>347.8099975585938</v>
+        <v>341.5400085449219</v>
       </c>
       <c r="C210" t="n">
-        <v>352.989990234375</v>
+        <v>361.8500061035156</v>
       </c>
       <c r="D210" t="n">
-        <v>334.5400085449219</v>
+        <v>338.7000122070312</v>
       </c>
       <c r="E210" t="n">
-        <v>336.760009765625</v>
+        <v>360.3099975585938</v>
       </c>
       <c r="F210" t="n">
-        <v>81616700</v>
+        <v>42000200</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B211" t="n">
-        <v>334.6300048828125</v>
+        <v>355.260009765625</v>
       </c>
       <c r="C211" t="n">
-        <v>349.2099914550781</v>
+        <v>359.5700073242188</v>
       </c>
       <c r="D211" t="n">
-        <v>328.8099975585938</v>
+        <v>344.8800048828125</v>
       </c>
       <c r="E211" t="n">
-        <v>346.3200073242188</v>
+        <v>351.510009765625</v>
       </c>
       <c r="F211" t="n">
-        <v>50585300</v>
+        <v>64235100</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B212" t="n">
-        <v>323.2099914550781</v>
+        <v>421.3900146484375</v>
       </c>
       <c r="C212" t="n">
-        <v>327.5</v>
+        <v>430.6000061035156</v>
       </c>
       <c r="D212" t="n">
-        <v>310</v>
+        <v>402.0400085449219</v>
       </c>
       <c r="E212" t="n">
-        <v>311.8599853515625</v>
+        <v>409.489990234375</v>
       </c>
       <c r="F212" t="n">
-        <v>43002500</v>
+        <v>87732200</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="B213" t="n">
-        <v>337.1099853515625</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="C213" t="n">
-        <v>340.1700134277344</v>
+        <v>421.7099914550781</v>
       </c>
       <c r="D213" t="n">
-        <v>318.8599853515625</v>
+        <v>401.0799865722656</v>
       </c>
       <c r="E213" t="n">
-        <v>326.5799865722656</v>
+        <v>417.0700073242188</v>
       </c>
       <c r="F213" t="n">
-        <v>44704400</v>
+        <v>44885500</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="B214" t="n">
-        <v>354.489990234375</v>
+        <v>455.1900024414062</v>
       </c>
       <c r="C214" t="n">
-        <v>354.9599914550781</v>
+        <v>456.2900085449219</v>
       </c>
       <c r="D214" t="n">
-        <v>332.6000061035156</v>
+        <v>418.2900085449219</v>
       </c>
       <c r="E214" t="n">
-        <v>341.3599853515625</v>
+        <v>418.5899963378906</v>
       </c>
       <c r="F214" t="n">
-        <v>42115300</v>
+        <v>58134900</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="B215" t="n">
-        <v>360.5400085449219</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="C215" t="n">
-        <v>362.7900085449219</v>
+        <v>469.2200012207031</v>
       </c>
       <c r="D215" t="n">
-        <v>349.25</v>
+        <v>450.8800048828125</v>
       </c>
       <c r="E215" t="n">
-        <v>351.8699951171875</v>
+        <v>460.5499877929688</v>
       </c>
       <c r="F215" t="n">
-        <v>34279200</v>
+        <v>46085400</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B216" t="n">
-        <v>341.5400085449219</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="C216" t="n">
-        <v>361.8500061035156</v>
+        <v>458.7999877929688</v>
       </c>
       <c r="D216" t="n">
-        <v>338.7000122070312</v>
+        <v>426.1099853515625</v>
       </c>
       <c r="E216" t="n">
-        <v>360.3099975585938</v>
+        <v>449.25</v>
       </c>
       <c r="F216" t="n">
-        <v>42000200</v>
+        <v>39140100</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="B217" t="n">
-        <v>355.260009765625</v>
+        <v>445.5</v>
       </c>
       <c r="C217" t="n">
-        <v>359.5700073242188</v>
+        <v>459.5</v>
       </c>
       <c r="D217" t="n">
-        <v>344.8800048828125</v>
+        <v>432.6499938964844</v>
       </c>
       <c r="E217" t="n">
-        <v>351.510009765625</v>
+        <v>457.0400085449219</v>
       </c>
       <c r="F217" t="n">
-        <v>64235100</v>
+        <v>30423400</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="B218" t="n">
-        <v>421.3900146484375</v>
+        <v>449.7000122070312</v>
       </c>
       <c r="C218" t="n">
-        <v>430.6000061035156</v>
+        <v>453.3099975585938</v>
       </c>
       <c r="D218" t="n">
-        <v>402.0400085449219</v>
+        <v>435.6799926757812</v>
       </c>
       <c r="E218" t="n">
-        <v>409.489990234375</v>
+        <v>440.6000061035156</v>
       </c>
       <c r="F218" t="n">
-        <v>87732200</v>
+        <v>26113600</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="B219" t="n">
-        <v>408.4599914550781</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="C219" t="n">
-        <v>421.7099914550781</v>
+        <v>439</v>
       </c>
       <c r="D219" t="n">
-        <v>401.0799865722656</v>
+        <v>423.3599853515625</v>
       </c>
       <c r="E219" t="n">
-        <v>417.0700073242188</v>
+        <v>433.3399963378906</v>
       </c>
       <c r="F219" t="n">
-        <v>44885500</v>
+        <v>29131600</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="B220" t="n">
-        <v>455.1900024414062</v>
+        <v>420.989990234375</v>
       </c>
       <c r="C220" t="n">
-        <v>456.2900085449219</v>
+        <v>438.7999877929688</v>
       </c>
       <c r="D220" t="n">
-        <v>418.2900085449219</v>
+        <v>410.7099914550781</v>
       </c>
       <c r="E220" t="n">
-        <v>418.5899963378906</v>
+        <v>429.5</v>
       </c>
       <c r="F220" t="n">
-        <v>58134900</v>
+        <v>28432100</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B221" t="n">
-        <v>458.7900085449219</v>
+        <v>414.0499877929688</v>
       </c>
       <c r="C221" t="n">
-        <v>469.2200012207031</v>
+        <v>428.75</v>
       </c>
       <c r="D221" t="n">
-        <v>450.8800048828125</v>
+        <v>393.3599853515625</v>
       </c>
       <c r="E221" t="n">
-        <v>460.5499877929688</v>
+        <v>412.6000061035156</v>
       </c>
       <c r="F221" t="n">
-        <v>46085400</v>
+        <v>38756900</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B222" t="n">
-        <v>448.2900085449219</v>
+        <v>447.5799865722656</v>
       </c>
       <c r="C222" t="n">
-        <v>458.7999877929688</v>
+        <v>449.3900146484375</v>
       </c>
       <c r="D222" t="n">
-        <v>426.1099853515625</v>
+        <v>426.0499877929688</v>
       </c>
       <c r="E222" t="n">
-        <v>449.25</v>
+        <v>428.0400085449219</v>
       </c>
       <c r="F222" t="n">
-        <v>39140100</v>
+        <v>36137500</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B223" t="n">
-        <v>445.5</v>
+        <v>449.5899963378906</v>
       </c>
       <c r="C223" t="n">
-        <v>459.5</v>
+        <v>451.2000122070312</v>
       </c>
       <c r="D223" t="n">
-        <v>432.6499938964844</v>
+        <v>431.6000061035156</v>
       </c>
       <c r="E223" t="n">
-        <v>457.0400085449219</v>
+        <v>441.989990234375</v>
       </c>
       <c r="F223" t="n">
-        <v>30423400</v>
+        <v>27252000</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B224" t="n">
-        <v>449.7000122070312</v>
+        <v>467.510009765625</v>
       </c>
       <c r="C224" t="n">
-        <v>453.3099975585938</v>
+        <v>481.4100036621094</v>
       </c>
       <c r="D224" t="n">
-        <v>435.6799926757812</v>
+        <v>461.7099914550781</v>
       </c>
       <c r="E224" t="n">
-        <v>440.6000061035156</v>
+        <v>469.8399963378906</v>
       </c>
       <c r="F224" t="n">
-        <v>26113600</v>
+        <v>34758600</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B225" t="n">
-        <v>424.1000061035156</v>
+        <v>503.8900146484375</v>
       </c>
       <c r="C225" t="n">
-        <v>439</v>
+        <v>506.9599914550781</v>
       </c>
       <c r="D225" t="n">
-        <v>423.3599853515625</v>
+        <v>480.2300109863281</v>
       </c>
       <c r="E225" t="n">
-        <v>433.3399963378906</v>
+        <v>484.739990234375</v>
       </c>
       <c r="F225" t="n">
-        <v>29131600</v>
+        <v>38473800</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B226" t="n">
-        <v>420.989990234375</v>
+        <v>495.5400085449219</v>
       </c>
       <c r="C226" t="n">
-        <v>438.7999877929688</v>
+        <v>510.2099914550781</v>
       </c>
       <c r="D226" t="n">
-        <v>410.7099914550781</v>
+        <v>486.6600036621094</v>
       </c>
       <c r="E226" t="n">
-        <v>429.5</v>
+        <v>508</v>
       </c>
       <c r="F226" t="n">
-        <v>28432100</v>
+        <v>27589300</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B227" t="n">
-        <v>414.0499877929688</v>
+        <v>518.0900268554688</v>
       </c>
       <c r="C227" t="n">
-        <v>428.75</v>
+        <v>527.2000122070312</v>
       </c>
       <c r="D227" t="n">
-        <v>393.3599853515625</v>
+        <v>493.5199890136719</v>
       </c>
       <c r="E227" t="n">
-        <v>412.6000061035156</v>
+        <v>499</v>
       </c>
       <c r="F227" t="n">
-        <v>38756900</v>
+        <v>31438500</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B228" t="n">
-        <v>447.5799865722656</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="C228" t="n">
-        <v>449.3900146484375</v>
+        <v>522</v>
       </c>
       <c r="D228" t="n">
-        <v>426.0499877929688</v>
+        <v>503.4299926757812</v>
       </c>
       <c r="E228" t="n">
-        <v>428.0400085449219</v>
+        <v>520.7999877929688</v>
       </c>
       <c r="F228" t="n">
-        <v>36137500</v>
+        <v>30803200</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="B229" t="n">
-        <v>449.5899963378906</v>
+        <v>510.1300048828125</v>
       </c>
       <c r="C229" t="n">
-        <v>451.2000122070312</v>
+        <v>517.5</v>
       </c>
       <c r="D229" t="n">
-        <v>431.6000061035156</v>
+        <v>486.7999877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>441.989990234375</v>
+        <v>500.1600036621094</v>
       </c>
       <c r="F229" t="n">
-        <v>27252000</v>
+        <v>33309200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="B230" t="n">
-        <v>467.510009765625</v>
+        <v>521.5399780273438</v>
       </c>
       <c r="C230" t="n">
-        <v>481.4100036621094</v>
+        <v>522.489990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>461.7099914550781</v>
+        <v>501.2200012207031</v>
       </c>
       <c r="E230" t="n">
-        <v>469.8399963378906</v>
+        <v>506.2999877929688</v>
       </c>
       <c r="F230" t="n">
-        <v>34758600</v>
+        <v>24293200</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="B231" t="n">
-        <v>503.8900146484375</v>
+        <v>542.52001953125</v>
       </c>
       <c r="C231" t="n">
-        <v>506.9599914550781</v>
+        <v>546.4400024414062</v>
       </c>
       <c r="D231" t="n">
-        <v>480.2300109863281</v>
+        <v>524.2999877929688</v>
       </c>
       <c r="E231" t="n">
-        <v>484.739990234375</v>
+        <v>533.75</v>
       </c>
       <c r="F231" t="n">
-        <v>38473800</v>
+        <v>29411100</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="B232" t="n">
-        <v>495.5400085449219</v>
+        <v>523.2000122070312</v>
       </c>
       <c r="C232" t="n">
-        <v>510.2099914550781</v>
+        <v>532.1900024414062</v>
       </c>
       <c r="D232" t="n">
-        <v>486.6600036621094</v>
+        <v>499.8699951171875</v>
       </c>
       <c r="E232" t="n">
-        <v>508</v>
+        <v>514.75</v>
       </c>
       <c r="F232" t="n">
-        <v>27589300</v>
+        <v>29110000</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B233" t="n">
-        <v>518.0900268554688</v>
+        <v>466.3800048828125</v>
       </c>
       <c r="C233" t="n">
-        <v>527.2000122070312</v>
+        <v>505.6199951171875</v>
       </c>
       <c r="D233" t="n">
-        <v>493.5199890136719</v>
+        <v>463.9500122070312</v>
       </c>
       <c r="E233" t="n">
-        <v>499</v>
+        <v>499.5299987792969</v>
       </c>
       <c r="F233" t="n">
-        <v>31438500</v>
+        <v>46900600</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B234" t="n">
-        <v>516.0999755859375</v>
+        <v>490.3299865722656</v>
       </c>
       <c r="C234" t="n">
-        <v>522</v>
+        <v>494.9700012207031</v>
       </c>
       <c r="D234" t="n">
-        <v>503.4299926757812</v>
+        <v>477.7099914550781</v>
       </c>
       <c r="E234" t="n">
-        <v>520.7999877929688</v>
+        <v>485</v>
       </c>
       <c r="F234" t="n">
-        <v>30803200</v>
+        <v>25158800</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B235" t="n">
-        <v>510.1300048828125</v>
+        <v>475.510009765625</v>
       </c>
       <c r="C235" t="n">
-        <v>517.5</v>
+        <v>505</v>
       </c>
       <c r="D235" t="n">
-        <v>486.7999877929688</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="E235" t="n">
-        <v>500.1600036621094</v>
+        <v>502.75</v>
       </c>
       <c r="F235" t="n">
-        <v>33309200</v>
+        <v>37799800</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B236" t="n">
-        <v>521.5399780273438</v>
+        <v>452.3999938964844</v>
       </c>
       <c r="C236" t="n">
-        <v>522.489990234375</v>
+        <v>477.4500122070312</v>
       </c>
       <c r="D236" t="n">
-        <v>501.2200012207031</v>
+        <v>448.3299865722656</v>
       </c>
       <c r="E236" t="n">
-        <v>506.2999877929688</v>
+        <v>467.9700012207031</v>
       </c>
       <c r="F236" t="n">
-        <v>24293200</v>
+        <v>27777400</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B237" t="n">
-        <v>542.52001953125</v>
+        <v>488.4500122070312</v>
       </c>
       <c r="C237" t="n">
-        <v>546.4400024414062</v>
+        <v>490.4599914550781</v>
       </c>
       <c r="D237" t="n">
-        <v>524.2999877929688</v>
+        <v>458.0199890136719</v>
       </c>
       <c r="E237" t="n">
-        <v>533.75</v>
+        <v>461.6000061035156</v>
       </c>
       <c r="F237" t="n">
-        <v>29411100</v>
+        <v>30463100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B238" t="n">
-        <v>523.2000122070312</v>
+        <v>511.5700073242188</v>
       </c>
       <c r="C238" t="n">
-        <v>532.1900024414062</v>
+        <v>521.7100219726562</v>
       </c>
       <c r="D238" t="n">
-        <v>499.8699951171875</v>
+        <v>494</v>
       </c>
       <c r="E238" t="n">
-        <v>514.75</v>
+        <v>499.6900024414062</v>
       </c>
       <c r="F238" t="n">
-        <v>29110000</v>
+        <v>31553100</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="B239" t="n">
-        <v>466.3800048828125</v>
+        <v>547.260009765625</v>
       </c>
       <c r="C239" t="n">
-        <v>505.6199951171875</v>
+        <v>558.3699951171875</v>
       </c>
       <c r="D239" t="n">
-        <v>463.9500122070312</v>
+        <v>530.5</v>
       </c>
       <c r="E239" t="n">
-        <v>499.5299987792969</v>
+        <v>535.75</v>
       </c>
       <c r="F239" t="n">
-        <v>46900600</v>
+        <v>33482400</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="B240" t="n">
-        <v>490.3299865722656</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="C240" t="n">
-        <v>494.9700012207031</v>
+        <v>548.9500122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>477.7099914550781</v>
+        <v>507.25</v>
       </c>
       <c r="E240" t="n">
-        <v>485</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="F240" t="n">
-        <v>25158800</v>
+        <v>28411700</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="B241" t="n">
-        <v>475.510009765625</v>
+        <v>512.47998046875</v>
       </c>
       <c r="C241" t="n">
-        <v>505</v>
+        <v>532.5</v>
       </c>
       <c r="D241" t="n">
-        <v>437.2300109863281</v>
+        <v>507.2999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>502.75</v>
+        <v>529.6599731445312</v>
       </c>
       <c r="F241" t="n">
-        <v>37799800</v>
+        <v>27085300</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="B242" t="n">
-        <v>452.3999938964844</v>
+        <v>537.3699951171875</v>
       </c>
       <c r="C242" t="n">
-        <v>477.4500122070312</v>
+        <v>539.6900024414062</v>
       </c>
       <c r="D242" t="n">
-        <v>448.3299865722656</v>
+        <v>526.3200073242188</v>
       </c>
       <c r="E242" t="n">
-        <v>467.9700012207031</v>
+        <v>531.5800170898438</v>
       </c>
       <c r="F242" t="n">
-        <v>27777400</v>
+        <v>43805600</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="B243" t="n">
-        <v>488.4500122070312</v>
+        <v>551.6300048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>490.4599914550781</v>
+        <v>562.989990234375</v>
       </c>
       <c r="D243" t="n">
-        <v>458.0199890136719</v>
+        <v>535.7100219726562</v>
       </c>
       <c r="E243" t="n">
-        <v>461.6000061035156</v>
+        <v>545.5</v>
       </c>
       <c r="F243" t="n">
-        <v>30463100</v>
+        <v>25983200</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="B244" t="n">
-        <v>511.5700073242188</v>
+        <v>519.8499755859375</v>
       </c>
       <c r="C244" t="n">
-        <v>521.7100219726562</v>
+        <v>528.489990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>494</v>
+        <v>506.8099975585938</v>
       </c>
       <c r="E244" t="n">
-        <v>499.6900024414062</v>
+        <v>509.0799865722656</v>
       </c>
       <c r="F244" t="n">
-        <v>31553100</v>
+        <v>30196800</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="B245" t="n">
-        <v>547.260009765625</v>
+        <v>519.739990234375</v>
       </c>
       <c r="C245" t="n">
-        <v>558.3699951171875</v>
+        <v>524.9600219726562</v>
       </c>
       <c r="D245" t="n">
-        <v>530.5</v>
+        <v>503.5</v>
       </c>
       <c r="E245" t="n">
-        <v>535.75</v>
+        <v>520.8200073242188</v>
       </c>
       <c r="F245" t="n">
-        <v>33482400</v>
+        <v>26548300</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="B246" t="n">
-        <v>507.2900085449219</v>
+        <v>532.5700073242188</v>
       </c>
       <c r="C246" t="n">
-        <v>548.9500122070312</v>
+        <v>550.8800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>507.25</v>
+        <v>507</v>
       </c>
       <c r="E246" t="n">
-        <v>546.8900146484375</v>
+        <v>543.9299926757812</v>
       </c>
       <c r="F246" t="n">
-        <v>28411700</v>
+        <v>27031300</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="B247" t="n">
-        <v>512.47998046875</v>
+        <v>521.5800170898438</v>
       </c>
       <c r="C247" t="n">
-        <v>532.5</v>
+        <v>525.1099853515625</v>
       </c>
       <c r="D247" t="n">
-        <v>507.2999877929688</v>
+        <v>502.6099853515625</v>
       </c>
       <c r="E247" t="n">
-        <v>529.6599731445312</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="F247" t="n">
-        <v>27085300</v>
+        <v>52705100</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B248" t="n">
-        <v>537.3699951171875</v>
+        <v>539.489990234375</v>
       </c>
       <c r="C248" t="n">
-        <v>539.6900024414062</v>
+        <v>542.1900024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>526.3200073242188</v>
+        <v>495.3500061035156</v>
       </c>
       <c r="E248" t="n">
-        <v>531.5800170898438</v>
+        <v>522.8400268554688</v>
       </c>
       <c r="F248" t="n">
-        <v>43805600</v>
+        <v>26671000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B249" t="n">
-        <v>551.6300048828125</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="C249" t="n">
-        <v>562.989990234375</v>
+        <v>584.72998046875</v>
       </c>
       <c r="D249" t="n">
-        <v>535.7100219726562</v>
+        <v>545.5700073242188</v>
       </c>
       <c r="E249" t="n">
-        <v>545.5</v>
+        <v>545.5700073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>25983200</v>
+        <v>34488500</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B250" t="n">
-        <v>519.8499755859375</v>
+        <v>540.8800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>528.489990234375</v>
+        <v>564.0900268554688</v>
       </c>
       <c r="D250" t="n">
-        <v>506.8099975585938</v>
+        <v>538.739990234375</v>
       </c>
       <c r="E250" t="n">
-        <v>509.0799865722656</v>
+        <v>557.530029296875</v>
       </c>
       <c r="F250" t="n">
-        <v>30196800</v>
+        <v>28326800</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46205</v>
       </c>
       <c r="B251" t="n">
-        <v>519.739990234375</v>
+        <v>517.8200073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>524.9600219726562</v>
+        <v>547.6500244140625</v>
       </c>
       <c r="D251" t="n">
-        <v>503.5</v>
+        <v>506</v>
       </c>
       <c r="E251" t="n">
-        <v>520.8200073242188</v>
+        <v>538.1599731445312</v>
       </c>
       <c r="F251" t="n">
-        <v>26548300</v>
+        <v>28142500</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B252" t="n">
-        <v>532.5700073242188</v>
+        <v>552.0499877929688</v>
       </c>
       <c r="C252" t="n">
-        <v>550.8800048828125</v>
+        <v>572.5</v>
       </c>
       <c r="D252" t="n">
-        <v>507</v>
+        <v>527.0399780273438</v>
       </c>
       <c r="E252" t="n">
-        <v>543.9299926757812</v>
+        <v>535.2000122070312</v>
       </c>
       <c r="F252" t="n">
-        <v>25777021</v>
+        <v>29556990</v>
       </c>
     </row>
   </sheetData>
